--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -10,9 +10,9 @@
     <sheet name="AI Agent Generate" sheetId="1" r:id="rId1"/>
     <sheet name="Static Analysis (reproduction)" sheetId="2" r:id="rId2"/>
     <sheet name="automatic testing" sheetId="3" r:id="rId3"/>
-    <sheet name="LAMT vs RT" sheetId="4" r:id="rId4"/>
-    <sheet name="LAMT vs SAMT1" sheetId="5" r:id="rId5"/>
-    <sheet name="LAMT vs SAMT2" sheetId="6" r:id="rId6"/>
+    <sheet name="LMT vs RT" sheetId="4" r:id="rId4"/>
+    <sheet name="LMT vs SAMT1" sheetId="5" r:id="rId5"/>
+    <sheet name="LMT vs SAMT2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="47">
   <si>
     <t>HarmonyOS App</t>
   </si>
@@ -152,6 +152,27 @@
   </si>
   <si>
     <t>当前方法与原论文结果的对比</t>
+  </si>
+  <si>
+    <t>LLM PTG-based Testing SC</t>
+  </si>
+  <si>
+    <t>LLM PTG-based Testing PC</t>
+  </si>
+  <si>
+    <t>LLM PTG-based Testing AN</t>
+  </si>
+  <si>
+    <t>Random Testing SC</t>
+  </si>
+  <si>
+    <t>SA PTG-based Testing SC</t>
+  </si>
+  <si>
+    <t>SA PTG-based Testing PC</t>
+  </si>
+  <si>
+    <t>SA PTG-based Testing AN</t>
   </si>
 </sst>
 </file>
@@ -4387,7 +4408,7 @@
         <v>0.2</v>
       </c>
       <c r="L37" s="5">
-        <f t="shared" ref="L37:L43" si="7">AVERAGE(B37:K37)</f>
+        <f t="shared" ref="L37:L45" si="7">AVERAGE(B37:K37)</f>
         <v>0.2</v>
       </c>
     </row>
@@ -4660,7 +4681,7 @@
         <v>0.2</v>
       </c>
       <c r="L44" s="5">
-        <f>AVERAGE(B44:K44)</f>
+        <f t="shared" si="7"/>
         <v>0.23</v>
       </c>
     </row>
@@ -4699,7 +4720,7 @@
         <v>0.2</v>
       </c>
       <c r="L45" s="5">
-        <f>AVERAGE(B45:K45)</f>
+        <f t="shared" si="7"/>
         <v>0.2</v>
       </c>
     </row>
@@ -4785,7 +4806,7 @@
         <v>19</v>
       </c>
       <c r="L49" s="4">
-        <f t="shared" ref="L47:L53" si="8">AVERAGE(B49:K49)</f>
+        <f t="shared" ref="L47:L57" si="8">AVERAGE(B49:K49)</f>
         <v>29.2</v>
       </c>
     </row>
@@ -4980,7 +5001,7 @@
         <v>99</v>
       </c>
       <c r="L54" s="4">
-        <f>AVERAGE(B54:K54)</f>
+        <f t="shared" si="8"/>
         <v>135.6</v>
       </c>
     </row>
@@ -5019,7 +5040,7 @@
         <v>194</v>
       </c>
       <c r="L55" s="4">
-        <f>AVERAGE(B55:K55)</f>
+        <f t="shared" si="8"/>
         <v>139.9</v>
       </c>
     </row>
@@ -5058,7 +5079,7 @@
         <v>115</v>
       </c>
       <c r="L56" s="4">
-        <f>AVERAGE(B56:K56)</f>
+        <f t="shared" si="8"/>
         <v>136</v>
       </c>
     </row>
@@ -5097,7 +5118,7 @@
         <v>163</v>
       </c>
       <c r="L57" s="4">
-        <f>AVERAGE(B57:K57)</f>
+        <f t="shared" si="8"/>
         <v>213</v>
       </c>
     </row>
@@ -8052,16 +8073,16 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>33</v>
@@ -8325,22 +8346,22 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8587,10 +8608,10 @@
   <cols>
     <col min="2" max="2" width="32.2019230769231" customWidth="1"/>
     <col min="3" max="3" width="28.0480769230769" customWidth="1"/>
-    <col min="4" max="4" width="31.4038461538462" customWidth="1"/>
-    <col min="5" max="5" width="28.6826923076923" customWidth="1"/>
-    <col min="6" max="6" width="31.5673076923077" customWidth="1"/>
-    <col min="7" max="7" width="33.8173076923077" customWidth="1"/>
+    <col min="4" max="4" width="29.9615384615385" customWidth="1"/>
+    <col min="5" max="5" width="28.3653846153846" customWidth="1"/>
+    <col min="6" max="6" width="26.1153846153846" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8598,22 +8619,22 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7">

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="14060" firstSheet="2" activeTab="5"/>
+    <workbookView windowWidth="28260" windowHeight="14060"/>
   </bookViews>
   <sheets>
     <sheet name="AI Agent Generate" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="51">
   <si>
     <t>HarmonyOS App</t>
   </si>
@@ -50,36 +50,6 @@
   </si>
   <si>
     <t>#Pages</t>
-  </si>
-  <si>
-    <t>TP</t>
-  </si>
-  <si>
-    <t>FP</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>Prec.</t>
-  </si>
-  <si>
-    <t>FNR</t>
-  </si>
-  <si>
-    <t>HER</t>
-  </si>
-  <si>
-    <t>calls</t>
-  </si>
-  <si>
-    <t>prompt</t>
-  </si>
-  <si>
-    <t>completion</t>
-  </si>
-  <si>
-    <t>total usage</t>
   </si>
   <si>
     <t>HarmoneyOpenEye</t>
@@ -112,10 +82,43 @@
     <t>ArkTS-wphui1.0</t>
   </si>
   <si>
+    <t>calls</t>
+  </si>
+  <si>
+    <t>prompt</t>
+  </si>
+  <si>
+    <t>completion</t>
+  </si>
+  <si>
+    <t>total usage</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>FP</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>Prec.</t>
+  </si>
+  <si>
     <t>Recall</t>
   </si>
   <si>
-    <t>cost</t>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>HER</t>
+  </si>
+  <si>
+    <t>FNR</t>
   </si>
   <si>
     <t>Times(s)</t>
@@ -152,6 +155,15 @@
   </si>
   <si>
     <t>当前方法与原论文结果的对比</t>
+  </si>
+  <si>
+    <t>SA Model-based Testing SC*</t>
+  </si>
+  <si>
+    <t>SA Model-based Testing PC*</t>
+  </si>
+  <si>
+    <t>SA Model-based Testing AN*</t>
   </si>
   <si>
     <t>LLM PTG-based Testing SC</t>
@@ -798,7 +810,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -820,7 +832,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1351,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X100"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="32.5288461538462" customWidth="1"/>
@@ -1360,6 +1378,7 @@
     <col min="4" max="4" width="13.6153846153846" customWidth="1"/>
     <col min="5" max="5" width="11.8557692307692" customWidth="1"/>
     <col min="6" max="6" width="13.1346153846154" customWidth="1"/>
+    <col min="7" max="7" width="12.9230769230769"/>
     <col min="12" max="12" width="9.77884615384615" customWidth="1"/>
     <col min="13" max="14" width="9.13461538461539" customWidth="1"/>
     <col min="15" max="15" width="11.8557692307692" customWidth="1"/>
@@ -1367,565 +1386,56 @@
     <col min="17" max="17" width="12.3365384615385" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
+    <row r="1" s="1" customFormat="1"/>
     <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
-        <v>72</v>
-      </c>
-      <c r="C2">
-        <v>4135</v>
-      </c>
-      <c r="D2">
-        <v>616</v>
-      </c>
-      <c r="E2">
-        <v>126</v>
-      </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>13</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.8667</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.0625</v>
-      </c>
-      <c r="L2" s="2">
-        <v>0.1333</v>
-      </c>
-      <c r="M2">
-        <v>53</v>
-      </c>
-      <c r="N2">
-        <v>86181</v>
-      </c>
-      <c r="O2">
-        <v>2648</v>
-      </c>
-      <c r="P2">
-        <f t="shared" ref="P2:P11" si="0">N2+O2</f>
-        <v>88829</v>
-      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>37</v>
-      </c>
-      <c r="C3">
-        <v>4423</v>
-      </c>
-      <c r="D3">
-        <v>80</v>
-      </c>
-      <c r="E3">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>10</v>
-      </c>
-      <c r="H3">
-        <v>6</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.0588</v>
-      </c>
-      <c r="L3" s="2">
-        <v>0.375</v>
-      </c>
-      <c r="M3">
-        <v>55</v>
-      </c>
-      <c r="N3">
-        <v>96802</v>
-      </c>
-      <c r="O3">
-        <v>3496</v>
-      </c>
-      <c r="P3">
-        <f t="shared" si="0"/>
-        <v>100298</v>
-      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
-        <v>59</v>
-      </c>
-      <c r="C4">
-        <v>6544</v>
-      </c>
-      <c r="D4">
-        <v>1800</v>
-      </c>
-      <c r="E4">
-        <v>853</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
-      </c>
-      <c r="L4" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="M4">
-        <v>33</v>
-      </c>
-      <c r="N4">
-        <v>89110</v>
-      </c>
-      <c r="O4">
-        <v>2081</v>
-      </c>
-      <c r="P4">
-        <f t="shared" si="0"/>
-        <v>91191</v>
-      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
-        <v>65</v>
-      </c>
-      <c r="C5">
-        <v>16999</v>
-      </c>
-      <c r="D5">
-        <v>24</v>
-      </c>
-      <c r="E5">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>6</v>
-      </c>
-      <c r="G5">
-        <v>8</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.1111</v>
-      </c>
-      <c r="L5" s="2">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>22</v>
-      </c>
-      <c r="N5">
-        <v>60341</v>
-      </c>
-      <c r="O5">
-        <v>1403</v>
-      </c>
-      <c r="P5">
-        <f t="shared" si="0"/>
-        <v>61744</v>
-      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
-        <v>20</v>
-      </c>
-      <c r="C6">
-        <v>902</v>
-      </c>
-      <c r="D6">
-        <v>50</v>
-      </c>
-      <c r="E6">
-        <v>6</v>
-      </c>
-      <c r="F6">
-        <v>6</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>0.6667</v>
-      </c>
-      <c r="M6">
-        <v>15</v>
-      </c>
-      <c r="N6">
-        <v>17014</v>
-      </c>
-      <c r="O6">
-        <v>799</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="0"/>
-        <v>17813</v>
-      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>55</v>
-      </c>
-      <c r="C7">
-        <v>4483</v>
-      </c>
-      <c r="D7">
-        <v>1800</v>
-      </c>
-      <c r="E7">
-        <v>853</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0.8333</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.1429</v>
-      </c>
-      <c r="L7" s="2">
-        <v>0.1667</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
-      </c>
-      <c r="N7">
-        <v>43467</v>
-      </c>
-      <c r="O7">
-        <v>1181</v>
-      </c>
-      <c r="P7">
-        <f t="shared" si="0"/>
-        <v>44648</v>
-      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>21</v>
-      </c>
-      <c r="C8">
-        <v>1652</v>
-      </c>
-      <c r="D8">
-        <v>167</v>
-      </c>
-      <c r="E8">
-        <v>46</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>7</v>
-      </c>
-      <c r="N8">
-        <v>13643</v>
-      </c>
-      <c r="O8">
-        <v>547</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="0"/>
-        <v>14190</v>
-      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>1018</v>
-      </c>
-      <c r="D9">
-        <v>362</v>
-      </c>
-      <c r="E9">
-        <v>74</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>6</v>
-      </c>
-      <c r="N9">
-        <v>6133</v>
-      </c>
-      <c r="O9">
-        <v>240</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="0"/>
-        <v>6373</v>
-      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10">
-        <v>26</v>
-      </c>
-      <c r="C10">
-        <v>2383</v>
-      </c>
-      <c r="D10">
-        <v>21</v>
-      </c>
-      <c r="E10">
-        <v>13</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>1</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0</v>
-      </c>
-      <c r="L10" s="2">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>8</v>
-      </c>
-      <c r="N10">
-        <v>13522</v>
-      </c>
-      <c r="O10">
-        <v>474</v>
-      </c>
-      <c r="P10">
-        <f t="shared" si="0"/>
-        <v>13996</v>
-      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11">
-        <v>24</v>
-      </c>
-      <c r="C11">
-        <v>2280</v>
-      </c>
-      <c r="D11">
-        <v>33</v>
-      </c>
-      <c r="E11">
-        <v>15</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2">
-        <v>0</v>
-      </c>
-      <c r="L11" s="2">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>5</v>
-      </c>
-      <c r="N11">
-        <v>9529</v>
-      </c>
-      <c r="O11">
-        <v>184</v>
-      </c>
-      <c r="P11">
-        <f t="shared" si="0"/>
-        <v>9713</v>
-      </c>
+      <c r="J11" s="5"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:16">
       <c r="J12" s="5"/>
@@ -1949,40 +1459,20 @@
       <c r="F15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B16">
         <v>72</v>
@@ -1999,42 +1489,16 @@
       <c r="F16">
         <v>10</v>
       </c>
-      <c r="G16">
-        <v>15</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2">
-        <f>G16/(G16+I16)</f>
-        <v>0.9375</v>
-      </c>
-      <c r="L16" s="2">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>33</v>
-      </c>
-      <c r="N16">
-        <v>58594</v>
-      </c>
-      <c r="O16">
-        <v>3892</v>
-      </c>
-      <c r="P16">
-        <f>N16+O16</f>
-        <v>62486</v>
-      </c>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:24">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B17">
         <v>37</v>
@@ -2051,42 +1515,16 @@
       <c r="F17">
         <v>9</v>
       </c>
-      <c r="G17">
-        <v>12</v>
-      </c>
-      <c r="H17">
-        <v>3</v>
-      </c>
-      <c r="I17">
-        <v>1</v>
-      </c>
-      <c r="J17" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="K17" s="2">
-        <f t="shared" ref="K17:K25" si="1">G17/(G17+I17)</f>
-        <v>0.923076923076923</v>
-      </c>
-      <c r="L17" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="M17">
-        <v>34</v>
-      </c>
-      <c r="N17">
-        <v>68856</v>
-      </c>
-      <c r="O17">
-        <v>4547</v>
-      </c>
-      <c r="P17">
-        <f t="shared" ref="P17:P25" si="2">N17+O17</f>
-        <v>73403</v>
-      </c>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:24">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>59</v>
@@ -2103,42 +1541,16 @@
       <c r="F18">
         <v>6</v>
       </c>
-      <c r="G18">
-        <v>7</v>
-      </c>
-      <c r="H18">
-        <v>3</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="K18" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L18" s="2">
-        <v>0.3</v>
-      </c>
-      <c r="M18">
-        <v>20</v>
-      </c>
-      <c r="N18">
-        <v>59375</v>
-      </c>
-      <c r="O18">
-        <v>2949</v>
-      </c>
-      <c r="P18">
-        <f t="shared" si="2"/>
-        <v>62324</v>
-      </c>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:24">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>65</v>
@@ -2155,42 +1567,16 @@
       <c r="F19">
         <v>6</v>
       </c>
-      <c r="G19">
-        <v>9</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" s="2">
-        <v>1</v>
-      </c>
-      <c r="K19" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L19" s="2">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>13</v>
-      </c>
-      <c r="N19">
-        <v>40287</v>
-      </c>
-      <c r="O19">
-        <v>2494</v>
-      </c>
-      <c r="P19">
-        <f t="shared" si="2"/>
-        <v>42781</v>
-      </c>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:24">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <v>20</v>
@@ -2207,42 +1593,16 @@
       <c r="F20">
         <v>6</v>
       </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L20" s="2">
-        <v>0.6667</v>
-      </c>
-      <c r="M20">
-        <v>10</v>
-      </c>
-      <c r="N20">
-        <v>13015</v>
-      </c>
-      <c r="O20">
-        <v>1097</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="2"/>
-        <v>14112</v>
-      </c>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:24">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B21">
         <v>55</v>
@@ -2259,42 +1619,16 @@
       <c r="F21">
         <v>5</v>
       </c>
-      <c r="G21">
-        <v>6</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="J21" s="5">
-        <v>1</v>
-      </c>
-      <c r="K21" s="2">
-        <f t="shared" si="1"/>
-        <v>0.857142857142857</v>
-      </c>
-      <c r="L21" s="2">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>16</v>
-      </c>
-      <c r="N21">
-        <v>30026</v>
-      </c>
-      <c r="O21">
-        <v>1627</v>
-      </c>
-      <c r="P21">
-        <f t="shared" si="2"/>
-        <v>31653</v>
-      </c>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B22">
         <v>21</v>
@@ -2311,42 +1645,16 @@
       <c r="F22">
         <v>3</v>
       </c>
-      <c r="G22">
-        <v>3</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L22" s="2">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>4</v>
-      </c>
-      <c r="N22">
-        <v>8308</v>
-      </c>
-      <c r="O22">
-        <v>708</v>
-      </c>
-      <c r="P22">
-        <f t="shared" si="2"/>
-        <v>9016</v>
-      </c>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B23">
         <v>13</v>
@@ -2363,42 +1671,16 @@
       <c r="F23">
         <v>2</v>
       </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
-        <v>1</v>
-      </c>
-      <c r="K23" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L23" s="2">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>4</v>
-      </c>
-      <c r="N23">
-        <v>4804</v>
-      </c>
-      <c r="O23">
-        <v>322</v>
-      </c>
-      <c r="P23">
-        <f t="shared" si="2"/>
-        <v>5126</v>
-      </c>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:24">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B24">
         <v>26</v>
@@ -2415,42 +1697,16 @@
       <c r="F24">
         <v>2</v>
       </c>
-      <c r="G24">
-        <v>3</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2">
-        <v>1</v>
-      </c>
-      <c r="K24" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L24" s="2">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>5</v>
-      </c>
-      <c r="N24">
-        <v>9744</v>
-      </c>
-      <c r="O24">
-        <v>737</v>
-      </c>
-      <c r="P24">
-        <f t="shared" si="2"/>
-        <v>10481</v>
-      </c>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B25">
         <v>24</v>
@@ -2467,57 +1723,31 @@
       <c r="F25">
         <v>2</v>
       </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" s="2">
-        <v>1</v>
-      </c>
-      <c r="K25" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L25" s="2">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>3</v>
-      </c>
-      <c r="N25">
-        <v>5983</v>
-      </c>
-      <c r="O25">
-        <v>255</v>
-      </c>
-      <c r="P25">
-        <f t="shared" si="2"/>
-        <v>6238</v>
-      </c>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2538,22 +1768,24 @@
     </row>
     <row r="28" spans="1:24">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B28">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="C28">
-        <v>4135</v>
+        <v>65205</v>
       </c>
       <c r="D28">
-        <v>616</v>
+        <v>3979</v>
       </c>
       <c r="E28">
-        <v>126</v>
-      </c>
-      <c r="F28">
-        <v>10</v>
+        <f t="shared" ref="E28:E37" si="0">C28+D28</f>
+        <v>69184</v>
+      </c>
+      <c r="F28" s="10">
+        <f>C28*(2/1000000)+D28*(3/1000000)</f>
+        <v>0.142347</v>
       </c>
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
@@ -2561,22 +1793,24 @@
     </row>
     <row r="29" spans="1:24">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B29">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C29">
-        <v>4423</v>
+        <v>75812</v>
       </c>
       <c r="D29">
-        <v>80</v>
+        <v>4645</v>
       </c>
       <c r="E29">
-        <v>18</v>
-      </c>
-      <c r="F29">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>80457</v>
+      </c>
+      <c r="F29" s="10">
+        <f t="shared" ref="F29:F37" si="1">C29*(2/1000000)+D29*(3/1000000)</f>
+        <v>0.165559</v>
       </c>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
@@ -2584,22 +1818,24 @@
     </row>
     <row r="30" spans="1:24">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B30">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="C30">
-        <v>6544</v>
+        <v>63422</v>
       </c>
       <c r="D30">
-        <v>1800</v>
+        <v>3006</v>
       </c>
       <c r="E30">
-        <v>853</v>
-      </c>
-      <c r="F30">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>66428</v>
+      </c>
+      <c r="F30" s="10">
+        <f t="shared" si="1"/>
+        <v>0.135862</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
@@ -2607,22 +1843,24 @@
     </row>
     <row r="31" spans="1:24">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B31">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="C31">
-        <v>16999</v>
+        <v>42969</v>
       </c>
       <c r="D31">
-        <v>24</v>
+        <v>2566</v>
       </c>
       <c r="E31">
-        <v>8</v>
-      </c>
-      <c r="F31">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>45535</v>
+      </c>
+      <c r="F31" s="10">
+        <f t="shared" si="1"/>
+        <v>0.093636</v>
       </c>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
@@ -2630,22 +1868,24 @@
     </row>
     <row r="32" spans="1:24">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B32">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>902</v>
+        <v>15212</v>
       </c>
       <c r="D32">
-        <v>50</v>
+        <v>1207</v>
       </c>
       <c r="E32">
-        <v>6</v>
-      </c>
-      <c r="F32">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>16419</v>
+      </c>
+      <c r="F32" s="10">
+        <f t="shared" si="1"/>
+        <v>0.034045</v>
       </c>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
@@ -2653,22 +1893,24 @@
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B33">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C33">
-        <v>4483</v>
+        <v>33269</v>
       </c>
       <c r="D33">
-        <v>1800</v>
+        <v>1673</v>
       </c>
       <c r="E33">
-        <v>853</v>
-      </c>
-      <c r="F33">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>34942</v>
+      </c>
+      <c r="F33" s="10">
+        <f t="shared" si="1"/>
+        <v>0.071557</v>
       </c>
       <c r="R33" s="5"/>
       <c r="S33" s="2"/>
@@ -2676,22 +1918,24 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B34">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>1652</v>
+        <v>9001</v>
       </c>
       <c r="D34">
-        <v>167</v>
+        <v>739</v>
       </c>
       <c r="E34">
-        <v>46</v>
-      </c>
-      <c r="F34">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>9740</v>
+      </c>
+      <c r="F34" s="10">
+        <f t="shared" si="1"/>
+        <v>0.020219</v>
       </c>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
@@ -2699,22 +1943,24 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B35">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C35">
-        <v>1018</v>
+        <v>5752</v>
       </c>
       <c r="D35">
-        <v>362</v>
+        <v>322</v>
       </c>
       <c r="E35">
-        <v>74</v>
-      </c>
-      <c r="F35">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>6074</v>
+      </c>
+      <c r="F35" s="10">
+        <f t="shared" si="1"/>
+        <v>0.01247</v>
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
@@ -2722,22 +1968,24 @@
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B36">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>2383</v>
+        <v>10773</v>
       </c>
       <c r="D36">
-        <v>21</v>
+        <v>728</v>
       </c>
       <c r="E36">
-        <v>13</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>11501</v>
+      </c>
+      <c r="F36" s="10">
+        <f t="shared" si="1"/>
+        <v>0.02373</v>
       </c>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
@@ -2745,22 +1993,24 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B37">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C37">
-        <v>2280</v>
+        <v>6556</v>
       </c>
       <c r="D37">
-        <v>33</v>
+        <v>270</v>
       </c>
       <c r="E37">
-        <v>15</v>
-      </c>
-      <c r="F37">
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>6826</v>
+      </c>
+      <c r="F37" s="10">
+        <f t="shared" si="1"/>
+        <v>0.013922</v>
       </c>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -2771,27 +2021,30 @@
         <v>0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G39" t="s">
         <v>26</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>11</v>
+      <c r="H39" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B40">
         <v>15</v>
@@ -2803,43 +2056,53 @@
         <v>1</v>
       </c>
       <c r="E40" s="2">
+        <f>B40/(B40+C40)</f>
         <v>1</v>
       </c>
       <c r="F40" s="2">
-        <f t="shared" ref="F40:F49" si="3">B40/(B40+D40)</f>
+        <f t="shared" ref="F40:F49" si="2">B40/(B40+D40)</f>
         <v>0.9375</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="5">
+        <f>2*E40*F40/(E40+F40)</f>
+        <v>0.967741935483871</v>
+      </c>
+      <c r="H40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B41">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <f t="shared" ref="E41:E49" si="3">B41/(B41+C41)</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F41" s="2">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E41" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="F41" s="2">
-        <f t="shared" si="3"/>
-        <v>0.923076923076923</v>
-      </c>
-      <c r="G41" s="2">
+      <c r="G41" s="5">
+        <f t="shared" ref="G41:G49" si="4">2*E41*F41/(E41+F41)</f>
+        <v>0.896551724137931</v>
+      </c>
+      <c r="H41" s="2">
         <v>0.2</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B42">
         <v>7</v>
@@ -2851,91 +2114,111 @@
         <v>0</v>
       </c>
       <c r="E42" s="2">
+        <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
       <c r="F42" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="4"/>
+        <v>0.823529411764706</v>
+      </c>
+      <c r="H42" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43">
+        <v>8.6</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>1.4</v>
+      </c>
+      <c r="E43" s="2">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G42" s="2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20">
-      <c r="A43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B43">
-        <v>9</v>
-      </c>
-      <c r="C43">
-        <v>0</v>
-      </c>
-      <c r="D43">
-        <v>0</v>
-      </c>
-      <c r="E43" s="2">
-        <v>1</v>
-      </c>
       <c r="F43" s="2">
+        <f t="shared" si="2"/>
+        <v>0.86</v>
+      </c>
+      <c r="G43" s="5">
+        <f t="shared" si="4"/>
+        <v>0.924731182795699</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G43" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
-      <c r="A44" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44">
-        <v>3</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2">
+      <c r="F44" s="2">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="F44" s="2">
+      <c r="G44" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H44" s="2">
+        <v>0.6667</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45" s="2">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G44" s="2">
-        <v>0.6667</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20">
-      <c r="A45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B45">
-        <v>6</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" s="5">
-        <v>1</v>
-      </c>
       <c r="F45" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0.857142857142857</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="5">
+        <f t="shared" si="4"/>
+        <v>0.923076923076923</v>
+      </c>
+      <c r="H45" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B46">
         <v>3</v>
@@ -2947,19 +2230,24 @@
         <v>0</v>
       </c>
       <c r="E46" s="2">
-        <v>1</v>
-      </c>
-      <c r="F46" s="2">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G46" s="2">
+      <c r="F46" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G46" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H46" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B47">
         <v>2</v>
@@ -2971,19 +2259,24 @@
         <v>0</v>
       </c>
       <c r="E47" s="2">
-        <v>1</v>
-      </c>
-      <c r="F47" s="2">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G47" s="2">
+      <c r="F47" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G47" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H47" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B48">
         <v>3</v>
@@ -2995,19 +2288,24 @@
         <v>0</v>
       </c>
       <c r="E48" s="2">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G48" s="2">
+      <c r="F48" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G48" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H48" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -3019,35 +2317,40 @@
         <v>0</v>
       </c>
       <c r="E49" s="2">
-        <v>1</v>
-      </c>
-      <c r="F49" s="2">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="G49" s="2">
-        <v>0</v>
+      <c r="F49" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="G49" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H49" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="D50" s="9">
+        <f>AVERAGE(D40:D49)</f>
+        <v>0.34</v>
+      </c>
+      <c r="E50" s="5">
+        <f>AVERAGE(E40:E49)</f>
+        <v>0.95125</v>
+      </c>
+      <c r="F50" s="5">
+        <f>AVERAGE(F40:F49)</f>
+        <v>0.965464285714286</v>
+      </c>
+      <c r="G50" s="5">
+        <f>AVERAGE(G40:G49)</f>
+        <v>0.953563117725913</v>
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -3056,254 +2359,808 @@
       <c r="L51" s="1"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52">
-        <v>33</v>
-      </c>
-      <c r="C52">
-        <v>58594</v>
-      </c>
-      <c r="D52">
-        <v>3892</v>
-      </c>
-      <c r="E52">
-        <f t="shared" ref="E52:E61" si="4">C52+D52</f>
-        <v>62486</v>
-      </c>
-      <c r="F52" s="8">
-        <f>C52*(2/1000000)+D52*(3/1000000)</f>
-        <v>0.128864</v>
+      <c r="A52" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" t="s">
-        <v>17</v>
+      <c r="A53" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B53">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C53">
-        <v>68856</v>
+        <v>15</v>
       </c>
       <c r="D53">
-        <v>4547</v>
+        <v>15</v>
       </c>
       <c r="E53">
-        <f t="shared" si="4"/>
-        <v>73403</v>
-      </c>
-      <c r="F53" s="8">
-        <f t="shared" ref="F53:F61" si="5">C53*(2/1000000)+D53*(3/1000000)</f>
-        <v>0.151353</v>
+        <v>15</v>
+      </c>
+      <c r="F53">
+        <v>15</v>
+      </c>
+      <c r="G53">
+        <f>AVERAGE(B53:F53)</f>
+        <v>15</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" t="s">
-        <v>18</v>
+      <c r="A54" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B54">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>59375</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>2949</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <f t="shared" si="4"/>
-        <v>62324</v>
-      </c>
-      <c r="F54" s="8">
-        <f t="shared" si="5"/>
-        <v>0.127597</v>
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <f t="shared" ref="G54:G100" si="5">AVERAGE(B54:F54)</f>
+        <v>0</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" t="s">
-        <v>19</v>
+      <c r="A55" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B55">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>40287</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>2494</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <f t="shared" si="4"/>
-        <v>42781</v>
-      </c>
-      <c r="F55" s="8">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
         <f t="shared" si="5"/>
-        <v>0.088056</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56">
-        <v>10</v>
-      </c>
-      <c r="C56">
-        <v>13015</v>
-      </c>
-      <c r="D56">
-        <v>1097</v>
-      </c>
-      <c r="E56">
-        <f t="shared" si="4"/>
-        <v>14112</v>
-      </c>
-      <c r="F56" s="8">
-        <f t="shared" si="5"/>
-        <v>0.029321</v>
-      </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" t="s">
-        <v>21</v>
-      </c>
-      <c r="B57">
-        <v>16</v>
-      </c>
-      <c r="C57">
-        <v>30026</v>
-      </c>
-      <c r="D57">
-        <v>1627</v>
-      </c>
-      <c r="E57">
-        <f t="shared" si="4"/>
-        <v>31653</v>
-      </c>
-      <c r="F57" s="8">
-        <f t="shared" si="5"/>
-        <v>0.064933</v>
+      <c r="A57" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" t="s">
-        <v>22</v>
+      <c r="A58" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C58">
-        <v>8308</v>
+        <v>13</v>
       </c>
       <c r="D58">
-        <v>708</v>
+        <v>13</v>
       </c>
       <c r="E58">
-        <f t="shared" si="4"/>
-        <v>9016</v>
-      </c>
-      <c r="F58" s="8">
+        <v>13</v>
+      </c>
+      <c r="F58">
+        <v>13</v>
+      </c>
+      <c r="G58">
         <f t="shared" si="5"/>
-        <v>0.01874</v>
+        <v>13</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" t="s">
-        <v>23</v>
+      <c r="A59" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>4804</v>
+        <v>3</v>
       </c>
       <c r="D59">
-        <v>322</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <f t="shared" si="4"/>
-        <v>5126</v>
-      </c>
-      <c r="F59" s="8">
+        <v>3</v>
+      </c>
+      <c r="F59">
+        <v>3</v>
+      </c>
+      <c r="G59">
         <f t="shared" si="5"/>
-        <v>0.010574</v>
+        <v>3</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" t="s">
-        <v>24</v>
+      <c r="A60" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>9744</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>737</v>
+        <v>0</v>
       </c>
       <c r="E60">
-        <f t="shared" si="4"/>
-        <v>10481</v>
-      </c>
-      <c r="F60" s="8">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
         <f t="shared" si="5"/>
-        <v>0.021699</v>
+        <v>0</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" t="s">
-        <v>25</v>
-      </c>
-      <c r="B61">
-        <v>3</v>
-      </c>
-      <c r="C61">
-        <v>5983</v>
-      </c>
-      <c r="D61">
-        <v>255</v>
-      </c>
-      <c r="E61">
-        <f t="shared" si="4"/>
-        <v>6238</v>
-      </c>
-      <c r="F61" s="8">
-        <f t="shared" si="5"/>
-        <v>0.012731</v>
-      </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="A62" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="A63" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63">
+        <v>7</v>
+      </c>
+      <c r="C63">
+        <v>7</v>
+      </c>
+      <c r="D63">
+        <v>7</v>
+      </c>
+      <c r="E63">
+        <v>7</v>
+      </c>
+      <c r="F63">
+        <v>7</v>
+      </c>
+      <c r="G63">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="A64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="E64">
+        <v>3</v>
+      </c>
+      <c r="F64">
+        <v>3</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>9</v>
+      </c>
+      <c r="D68">
+        <v>8</v>
+      </c>
+      <c r="E68">
+        <v>9</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="5"/>
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <v>2</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="5"/>
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B73">
+        <v>3</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73">
+        <v>3</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B78">
+        <v>6</v>
+      </c>
+      <c r="C78">
+        <v>6</v>
+      </c>
+      <c r="D78">
+        <v>6</v>
+      </c>
+      <c r="E78">
+        <v>6</v>
+      </c>
+      <c r="F78">
+        <v>6</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83">
+        <v>3</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+      <c r="E83">
+        <v>3</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93">
+        <v>3</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93">
+        <v>3</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>1</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3314,264 +3171,345 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="32.3653846153846" customWidth="1"/>
     <col min="2" max="2" width="8.49038461538461" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5">
+        <f t="shared" ref="F2:F11" si="0">1-H2</f>
+        <v>0.5625</v>
+      </c>
+      <c r="G2" s="5">
+        <f>2*E2*F2/(E2+F2)</f>
+        <v>0.72</v>
+      </c>
+      <c r="H2" s="2">
+        <f>D2/(B2+D2)</f>
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G11" si="1">2*E3*F3/(E3+F3)</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H11" si="2">D3/(B3+D3)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="1"/>
+        <v>0.571428571428572</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" si="1"/>
+        <v>0.888888888888889</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>7</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="G2" s="2">
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G3" s="2">
-        <v>0.5294</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="G6" s="5">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.1111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.4286</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="E8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="E9" s="3">
         <v>1</v>
       </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
         <v>1</v>
       </c>
-      <c r="F10" s="3">
+      <c r="E10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="2">
-        <v>0.3333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
         <v>1</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G11" s="2">
-        <v>0</v>
+      <c r="G11" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="D12" s="9">
+        <f>AVERAGE(D2:D11)</f>
+        <v>2.7</v>
+      </c>
+      <c r="E12" s="5">
+        <f>AVERAGE(E2:E11)</f>
+        <v>0.975</v>
+      </c>
+      <c r="F12" s="5">
+        <f>AVERAGE(F2:F11)</f>
+        <v>0.742916666666667</v>
+      </c>
+      <c r="G12" s="5">
+        <f>AVERAGE(G2:G11)</f>
+        <v>0.824698412698413</v>
       </c>
     </row>
   </sheetData>
@@ -3583,7 +3521,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L158"/>
+  <dimension ref="A1:L187"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="10.8942307692308" customWidth="1"/>
@@ -3601,25 +3539,25 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3928,10 +3866,10 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="3"/>
@@ -4328,10 +4266,10 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -4726,10 +4664,10 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -4895,7 +4833,7 @@
       <c r="B52">
         <v>63</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="8">
         <v>120</v>
       </c>
       <c r="D52">
@@ -4934,7 +4872,7 @@
       <c r="B53">
         <v>94</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="8">
         <v>144</v>
       </c>
       <c r="D53">
@@ -5124,10 +5062,10 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -5522,10 +5460,10 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -5920,10 +5858,10 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -6321,10 +6259,10 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -6725,10 +6663,10 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C107" s="1"/>
       <c r="L107" s="4"/>
@@ -7128,10 +7066,10 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L119" s="4"/>
     </row>
@@ -7527,30 +7465,30 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -7793,30 +7731,30 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8048,6 +7986,517 @@
       <c r="G158" s="4">
         <v>86</v>
       </c>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="A165" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="A166">
+        <v>420</v>
+      </c>
+      <c r="B166" s="2">
+        <v>0.6577</v>
+      </c>
+      <c r="C166" s="2">
+        <v>0.6577</v>
+      </c>
+      <c r="D166" s="2">
+        <v>0.6895</v>
+      </c>
+      <c r="E166" s="2">
+        <v>0.662</v>
+      </c>
+      <c r="F166" s="2">
+        <v>0.6852</v>
+      </c>
+      <c r="G166" s="2">
+        <v>0.6634</v>
+      </c>
+      <c r="H166" s="2">
+        <v>0.6554</v>
+      </c>
+      <c r="I166" s="2">
+        <v>0.6554</v>
+      </c>
+      <c r="J166" s="2">
+        <v>0.6545</v>
+      </c>
+      <c r="K166" s="2">
+        <v>0.6852</v>
+      </c>
+      <c r="L166" s="5">
+        <f>AVERAGE(B166:K166)</f>
+        <v>0.6666</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="A167">
+        <v>480</v>
+      </c>
+      <c r="B167" s="2">
+        <v>0.6339</v>
+      </c>
+      <c r="C167" s="2">
+        <v>0.6559</v>
+      </c>
+      <c r="D167" s="2">
+        <v>0.6577</v>
+      </c>
+      <c r="E167" s="2">
+        <v>0.6313</v>
+      </c>
+      <c r="F167" s="2">
+        <v>0.6545</v>
+      </c>
+      <c r="G167" s="2">
+        <v>0.6298</v>
+      </c>
+      <c r="H167" s="2">
+        <v>0.6298</v>
+      </c>
+      <c r="I167" s="2">
+        <v>0.6313</v>
+      </c>
+      <c r="J167" s="2">
+        <v>0.6554</v>
+      </c>
+      <c r="K167" s="2">
+        <v>0.6339</v>
+      </c>
+      <c r="L167" s="5">
+        <f>AVERAGE(B167:K167)</f>
+        <v>0.64135</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
+      <c r="A168">
+        <v>540</v>
+      </c>
+      <c r="B168" s="2">
+        <v>0.6168</v>
+      </c>
+      <c r="C168" s="2">
+        <v>0.6577</v>
+      </c>
+      <c r="D168" s="2">
+        <v>0.6933</v>
+      </c>
+      <c r="E168" s="2">
+        <v>0.6313</v>
+      </c>
+      <c r="F168" s="2">
+        <v>0.6884</v>
+      </c>
+      <c r="G168" s="2">
+        <v>0.6903</v>
+      </c>
+      <c r="H168" s="2">
+        <v>0.6464</v>
+      </c>
+      <c r="I168" s="2">
+        <v>0.6325</v>
+      </c>
+      <c r="J168" s="2">
+        <v>0.6586</v>
+      </c>
+      <c r="K168" s="2">
+        <v>0.6734</v>
+      </c>
+      <c r="L168" s="5">
+        <f t="shared" ref="L167:L182" si="13">AVERAGE(B168:K168)</f>
+        <v>0.65887</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="A169">
+        <v>600</v>
+      </c>
+      <c r="B169" s="2">
+        <v>0.662</v>
+      </c>
+      <c r="C169" s="2">
+        <v>0.662</v>
+      </c>
+      <c r="D169" s="2">
+        <v>0.6769</v>
+      </c>
+      <c r="E169" s="2">
+        <v>0.6586</v>
+      </c>
+      <c r="F169" s="2">
+        <v>0.6668</v>
+      </c>
+      <c r="G169" s="2">
+        <v>0.6903</v>
+      </c>
+      <c r="H169" s="2">
+        <v>0.6586</v>
+      </c>
+      <c r="I169" s="2">
+        <v>0.6883</v>
+      </c>
+      <c r="J169" s="2">
+        <v>0.6672</v>
+      </c>
+      <c r="K169" s="2">
+        <v>0.6623</v>
+      </c>
+      <c r="L169" s="5">
+        <f t="shared" si="13"/>
+        <v>0.6693</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="B170" s="2"/>
+    </row>
+    <row r="171" spans="1:12">
+      <c r="A171" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
+      <c r="A172">
+        <v>420</v>
+      </c>
+      <c r="B172" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="C172" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D172" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="E172" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F172" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G172" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="H172" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I172" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J172" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="K172" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L172" s="5">
+        <f t="shared" si="13"/>
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
+      <c r="A173">
+        <v>480</v>
+      </c>
+      <c r="B173" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C173" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D173" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E173" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F173" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G173" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="H173" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I173" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J173" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="K173" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L173" s="5">
+        <f t="shared" si="13"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="A174">
+        <v>540</v>
+      </c>
+      <c r="B174" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C174" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D174" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E174" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F174" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G174" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="H174" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="I174" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J174" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="K174" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="L174" s="5">
+        <f t="shared" si="13"/>
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="A175">
+        <v>600</v>
+      </c>
+      <c r="B175" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="C175" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D175" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="E175" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="F175" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G175" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="H175" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="I175" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J175" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K175" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="L175" s="5">
+        <f t="shared" si="13"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
+      <c r="A177" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I177" s="3"/>
+    </row>
+    <row r="178" spans="1:12">
+      <c r="A178">
+        <v>420</v>
+      </c>
+      <c r="B178">
+        <v>25</v>
+      </c>
+      <c r="C178">
+        <v>26</v>
+      </c>
+      <c r="D178">
+        <v>26</v>
+      </c>
+      <c r="E178">
+        <v>31</v>
+      </c>
+      <c r="F178">
+        <v>27</v>
+      </c>
+      <c r="G178">
+        <v>30</v>
+      </c>
+      <c r="H178">
+        <v>26</v>
+      </c>
+      <c r="I178">
+        <v>24</v>
+      </c>
+      <c r="J178">
+        <v>25</v>
+      </c>
+      <c r="K178">
+        <v>27</v>
+      </c>
+      <c r="L178" s="4">
+        <f t="shared" si="13"/>
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
+      <c r="A179">
+        <v>480</v>
+      </c>
+      <c r="B179">
+        <v>27</v>
+      </c>
+      <c r="C179">
+        <v>45</v>
+      </c>
+      <c r="D179">
+        <v>28</v>
+      </c>
+      <c r="E179">
+        <v>27</v>
+      </c>
+      <c r="F179">
+        <v>27</v>
+      </c>
+      <c r="G179">
+        <v>27</v>
+      </c>
+      <c r="H179">
+        <v>27</v>
+      </c>
+      <c r="I179">
+        <v>27</v>
+      </c>
+      <c r="J179">
+        <v>35</v>
+      </c>
+      <c r="K179">
+        <v>27</v>
+      </c>
+      <c r="L179" s="4">
+        <f t="shared" si="13"/>
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
+      <c r="A180">
+        <v>540</v>
+      </c>
+      <c r="B180">
+        <v>35</v>
+      </c>
+      <c r="C180">
+        <v>30</v>
+      </c>
+      <c r="D180">
+        <v>49</v>
+      </c>
+      <c r="E180">
+        <v>29</v>
+      </c>
+      <c r="F180">
+        <v>31</v>
+      </c>
+      <c r="G180">
+        <v>30</v>
+      </c>
+      <c r="H180">
+        <v>52</v>
+      </c>
+      <c r="I180">
+        <v>52</v>
+      </c>
+      <c r="J180">
+        <v>29</v>
+      </c>
+      <c r="L180" s="4">
+        <f t="shared" si="13"/>
+        <v>37.4444444444444</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
+      <c r="A181">
+        <v>600</v>
+      </c>
+      <c r="B181">
+        <v>30</v>
+      </c>
+      <c r="C181">
+        <v>32</v>
+      </c>
+      <c r="D181">
+        <v>35</v>
+      </c>
+      <c r="E181">
+        <v>30</v>
+      </c>
+      <c r="F181">
+        <v>47</v>
+      </c>
+      <c r="G181">
+        <v>31</v>
+      </c>
+      <c r="H181">
+        <v>30</v>
+      </c>
+      <c r="I181">
+        <v>39</v>
+      </c>
+      <c r="J181">
+        <v>35</v>
+      </c>
+      <c r="K181">
+        <v>30</v>
+      </c>
+      <c r="L181" s="4">
+        <f t="shared" si="13"/>
+        <v>33.9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
+      <c r="B182" s="3"/>
+    </row>
+    <row r="183" spans="1:12">
+      <c r="B183" s="3"/>
+    </row>
+    <row r="184" spans="1:12">
+      <c r="B184" s="3"/>
+    </row>
+    <row r="185" spans="1:12">
+      <c r="B185" s="3"/>
+    </row>
+    <row r="186" spans="1:12">
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" spans="1:12">
+      <c r="B187" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8058,7 +8507,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="3" width="27.7211538461538" customWidth="1"/>
@@ -8070,25 +8519,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8320,6 +8769,15 @@
       <c r="G11" s="6">
         <v>213</v>
       </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="5">
+        <f>(B11-E11)/E11</f>
+        <v>0.295827679134573</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8343,25 +8801,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8616,25 +9074,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:7">

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="14060"/>
+    <workbookView windowWidth="26300" windowHeight="11780" firstSheet="2" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="AI Agent Generate" sheetId="1" r:id="rId1"/>
     <sheet name="Static Analysis (reproduction)" sheetId="2" r:id="rId2"/>
     <sheet name="automatic testing" sheetId="3" r:id="rId3"/>
     <sheet name="LMT vs RT" sheetId="4" r:id="rId4"/>
-    <sheet name="LMT vs SAMT1" sheetId="5" r:id="rId5"/>
+    <sheet name="LMT vs SAMT" sheetId="5" r:id="rId5"/>
     <sheet name="LMT vs SAMT2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -1489,9 +1489,6 @@
       <c r="F16">
         <v>10</v>
       </c>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -1515,9 +1512,6 @@
       <c r="F17">
         <v>9</v>
       </c>
-      <c r="G17"/>
-      <c r="H17"/>
-      <c r="I17"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -1541,9 +1535,6 @@
       <c r="F18">
         <v>6</v>
       </c>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
@@ -1567,9 +1558,6 @@
       <c r="F19">
         <v>6</v>
       </c>
-      <c r="G19"/>
-      <c r="H19"/>
-      <c r="I19"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -1593,9 +1581,6 @@
       <c r="F20">
         <v>6</v>
       </c>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -1619,9 +1604,6 @@
       <c r="F21">
         <v>5</v>
       </c>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
       <c r="J21" s="5"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -1645,9 +1627,6 @@
       <c r="F22">
         <v>3</v>
       </c>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -1671,9 +1650,6 @@
       <c r="F23">
         <v>2</v>
       </c>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -1697,9 +1673,6 @@
       <c r="F24">
         <v>2</v>
       </c>
-      <c r="G24"/>
-      <c r="H24"/>
-      <c r="I24"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
@@ -1723,9 +1696,6 @@
       <c r="F25">
         <v>2</v>
       </c>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -4,15 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26300" windowHeight="11780" firstSheet="2" activeTab="4"/>
+    <workbookView windowWidth="26300" windowHeight="11780" tabRatio="882" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="AI Agent Generate" sheetId="1" r:id="rId1"/>
-    <sheet name="Static Analysis (reproduction)" sheetId="2" r:id="rId2"/>
-    <sheet name="automatic testing" sheetId="3" r:id="rId3"/>
-    <sheet name="LMT vs RT" sheetId="4" r:id="rId4"/>
-    <sheet name="LMT vs SAMT" sheetId="5" r:id="rId5"/>
-    <sheet name="LMT vs SAMT2" sheetId="6" r:id="rId6"/>
+    <sheet name="dataset" sheetId="8" r:id="rId1"/>
+    <sheet name="DeepSeek Generate" sheetId="1" r:id="rId2"/>
+    <sheet name="ChatGPT Generate" sheetId="7" r:id="rId3"/>
+    <sheet name="Static Analysis (reproduction)" sheetId="2" r:id="rId4"/>
+    <sheet name="automatic testing" sheetId="3" r:id="rId5"/>
+    <sheet name="LMT vs RT" sheetId="4" r:id="rId6"/>
+    <sheet name="LMT vs SAMT" sheetId="5" r:id="rId7"/>
+    <sheet name="LMT vs SAMT2" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="52">
   <si>
     <t>HarmonyOS App</t>
   </si>
@@ -118,6 +120,9 @@
     <t>HER</t>
   </si>
   <si>
+    <t>AE</t>
+  </si>
+  <si>
     <t>FNR</t>
   </si>
   <si>
@@ -191,13 +196,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="9">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
+    <numFmt numFmtId="177" formatCode="&quot;US$&quot;#,##0.00_);[Red]\(&quot;US$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -810,7 +818,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -842,6 +850,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1369,7 +1389,242 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X100"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="36.0576923076923" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>72</v>
+      </c>
+      <c r="C2">
+        <v>4135</v>
+      </c>
+      <c r="D2">
+        <v>616</v>
+      </c>
+      <c r="E2">
+        <v>126</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>37</v>
+      </c>
+      <c r="C3">
+        <v>4423</v>
+      </c>
+      <c r="D3">
+        <v>80</v>
+      </c>
+      <c r="E3">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>59</v>
+      </c>
+      <c r="C4">
+        <v>6544</v>
+      </c>
+      <c r="D4">
+        <v>1800</v>
+      </c>
+      <c r="E4">
+        <v>853</v>
+      </c>
+      <c r="F4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>65</v>
+      </c>
+      <c r="C5">
+        <v>16999</v>
+      </c>
+      <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>902</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>55</v>
+      </c>
+      <c r="C7">
+        <v>4483</v>
+      </c>
+      <c r="D7">
+        <v>1800</v>
+      </c>
+      <c r="E7">
+        <v>853</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>1652</v>
+      </c>
+      <c r="D8">
+        <v>167</v>
+      </c>
+      <c r="E8">
+        <v>46</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>1018</v>
+      </c>
+      <c r="D9">
+        <v>362</v>
+      </c>
+      <c r="E9">
+        <v>74</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>2383</v>
+      </c>
+      <c r="D10">
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>2280</v>
+      </c>
+      <c r="D11">
+        <v>33</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:X75"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="32.5288461538462" customWidth="1"/>
@@ -1379,6 +1634,7 @@
     <col min="5" max="5" width="11.8557692307692" customWidth="1"/>
     <col min="6" max="6" width="13.1346153846154" customWidth="1"/>
     <col min="7" max="7" width="12.9230769230769"/>
+    <col min="8" max="8" width="13.3076923076923" customWidth="1"/>
     <col min="12" max="12" width="9.77884615384615" customWidth="1"/>
     <col min="13" max="14" width="9.13461538461539" customWidth="1"/>
     <col min="15" max="15" width="11.8557692307692" customWidth="1"/>
@@ -1386,53 +1642,274 @@
     <col min="17" max="17" width="12.3365384615385" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1"/>
+    <row r="1" s="1" customFormat="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1"/>
+      <c r="H1"/>
+    </row>
     <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>65205</v>
+      </c>
+      <c r="D2">
+        <v>3979</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ref="E2:E11" si="0">C2+D2</f>
+        <v>69184</v>
+      </c>
+      <c r="F2" s="13">
+        <f>C2*(2/1000000)+D2*(3/1000000)</f>
+        <v>0.142347</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>34</v>
+      </c>
+      <c r="C3">
+        <v>75812</v>
+      </c>
+      <c r="D3">
+        <v>4645</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>80457</v>
+      </c>
+      <c r="F3" s="13">
+        <f t="shared" ref="F3:F11" si="1">C3*(2/1000000)+D3*(3/1000000)</f>
+        <v>0.165559</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>63422</v>
+      </c>
+      <c r="D4">
+        <v>3006</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>66428</v>
+      </c>
+      <c r="F4" s="13">
+        <f t="shared" si="1"/>
+        <v>0.135862</v>
+      </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>42969</v>
+      </c>
+      <c r="D5">
+        <v>2566</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>45535</v>
+      </c>
+      <c r="F5" s="13">
+        <f t="shared" si="1"/>
+        <v>0.093636</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>15212</v>
+      </c>
+      <c r="D6">
+        <v>1207</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>16419</v>
+      </c>
+      <c r="F6" s="13">
+        <f t="shared" si="1"/>
+        <v>0.034045</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>33269</v>
+      </c>
+      <c r="D7">
+        <v>1673</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>34942</v>
+      </c>
+      <c r="F7" s="13">
+        <f t="shared" si="1"/>
+        <v>0.071557</v>
+      </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>9001</v>
+      </c>
+      <c r="D8">
+        <v>739</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>9740</v>
+      </c>
+      <c r="F8" s="13">
+        <f t="shared" si="1"/>
+        <v>0.020219</v>
+      </c>
       <c r="J8" s="5"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>5752</v>
+      </c>
+      <c r="D9">
+        <v>322</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>6074</v>
+      </c>
+      <c r="F9" s="13">
+        <f t="shared" si="1"/>
+        <v>0.01247</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>10773</v>
+      </c>
+      <c r="D10">
+        <v>728</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>11501</v>
+      </c>
+      <c r="F10" s="13">
+        <f t="shared" si="1"/>
+        <v>0.02373</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:16">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>6556</v>
+      </c>
+      <c r="D11">
+        <v>270</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>6826</v>
+      </c>
+      <c r="F11" s="13">
+        <f t="shared" si="1"/>
+        <v>0.013922</v>
+      </c>
       <c r="J11" s="5"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -1440,28 +1917,100 @@
     <row r="12" spans="1:16">
       <c r="J12" s="5"/>
     </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="12">
+        <v>15</v>
+      </c>
+      <c r="C14" s="12">
+        <v>0</v>
+      </c>
+      <c r="D14" s="12">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <f>B14/(B14+C14)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <f>B14/(B14+D14)</f>
+        <v>0.9375</v>
+      </c>
+      <c r="G14" s="5">
+        <f>2*E14*F14/(E14+F14)</f>
+        <v>0.967741935483871</v>
+      </c>
+      <c r="H14" s="2">
+        <f>(I14-B14)/I14</f>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>15</v>
+      </c>
+    </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="12">
+        <v>13</v>
+      </c>
+      <c r="C15" s="12">
         <v>3</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="D15" s="12">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" ref="E15:E23" si="2">B15/(B15+C15)</f>
+        <v>0.8125</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" ref="F14:F23" si="3">B15/(B15+D15)</f>
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" ref="G15:G23" si="4">2*E15*F15/(E15+F15)</f>
+        <v>0.896551724137931</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" ref="H15:H23" si="5">(I15-B15)/I15</f>
+        <v>0.1875</v>
+      </c>
+      <c r="I15" s="1">
+        <v>16</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1472,21 +2021,34 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16">
-        <v>72</v>
-      </c>
-      <c r="C16">
-        <v>4135</v>
-      </c>
-      <c r="D16">
-        <v>616</v>
-      </c>
-      <c r="E16">
-        <v>126</v>
-      </c>
-      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="B16" s="12">
+        <v>5</v>
+      </c>
+      <c r="C16" s="12">
+        <v>5</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="4"/>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="I16">
         <v>10</v>
       </c>
       <c r="J16" s="2"/>
@@ -1495,22 +2057,35 @@
     </row>
     <row r="17" spans="1:24">
       <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17">
-        <v>37</v>
-      </c>
-      <c r="C17">
-        <v>4423</v>
-      </c>
-      <c r="D17">
-        <v>80</v>
-      </c>
-      <c r="E17">
-        <v>18</v>
-      </c>
-      <c r="F17">
         <v>9</v>
+      </c>
+      <c r="B17" s="12">
+        <v>8.6</v>
+      </c>
+      <c r="C17" s="12">
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <v>1.4</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="3"/>
+        <v>0.86</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="4"/>
+        <v>0.924731182795699</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>8.6</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1518,22 +2093,35 @@
     </row>
     <row r="18" spans="1:24">
       <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18">
-        <v>59</v>
-      </c>
-      <c r="C18">
-        <v>6544</v>
-      </c>
-      <c r="D18">
-        <v>1800</v>
-      </c>
-      <c r="E18">
-        <v>853</v>
-      </c>
-      <c r="F18">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="B18" s="12">
+        <v>3</v>
+      </c>
+      <c r="C18" s="12">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -1541,21 +2129,34 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19">
-        <v>65</v>
-      </c>
-      <c r="C19">
-        <v>16999</v>
-      </c>
-      <c r="D19">
-        <v>24</v>
-      </c>
-      <c r="E19">
-        <v>8</v>
-      </c>
-      <c r="F19">
+        <v>11</v>
+      </c>
+      <c r="B19" s="12">
+        <v>6</v>
+      </c>
+      <c r="C19" s="12">
+        <v>0</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I19">
         <v>6</v>
       </c>
       <c r="J19" s="2"/>
@@ -1564,22 +2165,35 @@
     </row>
     <row r="20" spans="1:24">
       <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20">
-        <v>20</v>
-      </c>
-      <c r="C20">
-        <v>902</v>
-      </c>
-      <c r="D20">
-        <v>50</v>
-      </c>
-      <c r="E20">
-        <v>6</v>
-      </c>
-      <c r="F20">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="B20" s="12">
+        <v>3</v>
+      </c>
+      <c r="C20" s="12">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1587,22 +2201,35 @@
     </row>
     <row r="21" spans="1:24">
       <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21">
-        <v>55</v>
-      </c>
-      <c r="C21">
-        <v>4483</v>
-      </c>
-      <c r="D21">
-        <v>1800</v>
-      </c>
-      <c r="E21">
-        <v>853</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
+        <v>13</v>
+      </c>
+      <c r="B21" s="12">
+        <v>2</v>
+      </c>
+      <c r="C21" s="12">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="2"/>
@@ -1610,21 +2237,34 @@
     </row>
     <row r="22" spans="1:24">
       <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22">
-        <v>21</v>
-      </c>
-      <c r="C22">
-        <v>1652</v>
-      </c>
-      <c r="D22">
-        <v>167</v>
-      </c>
-      <c r="E22">
-        <v>46</v>
-      </c>
-      <c r="F22">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12">
+        <v>3</v>
+      </c>
+      <c r="C22" s="12">
+        <v>0</v>
+      </c>
+      <c r="D22" s="12">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>3</v>
       </c>
       <c r="J22" s="2"/>
@@ -1633,91 +2273,98 @@
     </row>
     <row r="23" spans="1:24">
       <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23">
-        <v>13</v>
-      </c>
-      <c r="C23">
-        <v>1018</v>
-      </c>
-      <c r="D23">
-        <v>362</v>
-      </c>
-      <c r="E23">
-        <v>74</v>
-      </c>
-      <c r="F23">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="B23" s="12">
+        <v>1</v>
+      </c>
+      <c r="C23" s="12">
+        <v>0</v>
+      </c>
+      <c r="D23" s="12">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:24">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24">
-        <v>26</v>
-      </c>
-      <c r="C24">
-        <v>2383</v>
-      </c>
-      <c r="D24">
-        <v>21</v>
-      </c>
-      <c r="E24">
-        <v>13</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
+      <c r="B24" s="14"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="5">
+        <f>AVERAGE(E14:E23)</f>
+        <v>0.93125</v>
+      </c>
+      <c r="F24" s="5">
+        <f>AVERAGE(F14:F23)</f>
+        <v>0.97975</v>
+      </c>
+      <c r="G24" s="5">
+        <f>AVERAGE(G14:G23)</f>
+        <v>0.945569150908417</v>
+      </c>
+      <c r="H24" s="5">
+        <f>AVERAGE(H14:H23)</f>
+        <v>0.10875</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:24">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-      <c r="C25">
-        <v>2280</v>
-      </c>
-      <c r="D25">
-        <v>33</v>
-      </c>
-      <c r="E25">
-        <v>15</v>
-      </c>
-      <c r="F25">
-        <v>2</v>
-      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
+    <row r="26" spans="1:24">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="27" spans="1:24">
       <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>15</v>
+      </c>
+      <c r="E27">
+        <v>15</v>
+      </c>
+      <c r="F27">
+        <v>15</v>
+      </c>
+      <c r="G27">
+        <f>AVERAGE(B27:F27)</f>
+        <v>15</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -1737,50 +2384,54 @@
       <c r="X27" s="1"/>
     </row>
     <row r="28" spans="1:24">
-      <c r="A28" t="s">
-        <v>6</v>
+      <c r="A28" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B28">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>65205</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>3979</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <f t="shared" ref="E28:E37" si="0">C28+D28</f>
-        <v>69184</v>
-      </c>
-      <c r="F28" s="10">
-        <f>C28*(2/1000000)+D28*(3/1000000)</f>
-        <v>0.142347</v>
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <f t="shared" ref="G28:G74" si="6">AVERAGE(B28:F28)</f>
+        <v>0</v>
       </c>
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
     </row>
     <row r="29" spans="1:24">
-      <c r="A29" t="s">
-        <v>7</v>
+      <c r="A29" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B29">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>75812</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>4645</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <f t="shared" si="0"/>
-        <v>80457</v>
-      </c>
-      <c r="F29" s="10">
-        <f t="shared" ref="F29:F37" si="1">C29*(2/1000000)+D29*(3/1000000)</f>
-        <v>0.165559</v>
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
@@ -1788,124 +2439,115 @@
     </row>
     <row r="30" spans="1:24">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B30">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C30">
-        <v>63422</v>
+        <v>15</v>
       </c>
       <c r="D30">
-        <v>3006</v>
+        <v>15</v>
       </c>
       <c r="E30">
-        <f t="shared" si="0"/>
-        <v>66428</v>
-      </c>
-      <c r="F30" s="10">
-        <f t="shared" si="1"/>
-        <v>0.135862</v>
+        <v>15</v>
+      </c>
+      <c r="F30">
+        <v>15</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="6"/>
+        <v>15</v>
       </c>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31">
-        <v>13</v>
-      </c>
-      <c r="C31">
-        <v>42969</v>
-      </c>
-      <c r="D31">
-        <v>2566</v>
-      </c>
-      <c r="E31">
-        <f t="shared" si="0"/>
-        <v>45535</v>
-      </c>
-      <c r="F31" s="10">
-        <f t="shared" si="1"/>
-        <v>0.093636</v>
+      <c r="A31" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" t="s">
-        <v>10</v>
+      <c r="A32" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C32">
-        <v>15212</v>
+        <v>13</v>
       </c>
       <c r="D32">
-        <v>1207</v>
+        <v>13</v>
       </c>
       <c r="E32">
-        <f t="shared" si="0"/>
-        <v>16419</v>
-      </c>
-      <c r="F32" s="10">
-        <f t="shared" si="1"/>
-        <v>0.034045</v>
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <v>13</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="6"/>
+        <v>13</v>
       </c>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
     </row>
     <row r="33" spans="1:20">
-      <c r="A33" t="s">
-        <v>11</v>
+      <c r="A33" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B33">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>33269</v>
+        <v>3</v>
       </c>
       <c r="D33">
-        <v>1673</v>
+        <v>3</v>
       </c>
       <c r="E33">
-        <f t="shared" si="0"/>
-        <v>34942</v>
-      </c>
-      <c r="F33" s="10">
-        <f t="shared" si="1"/>
-        <v>0.071557</v>
+        <v>3</v>
+      </c>
+      <c r="F33">
+        <v>3</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="R33" s="5"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
     </row>
     <row r="34" spans="1:20">
-      <c r="A34" t="s">
-        <v>12</v>
+      <c r="A34" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>9001</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>739</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <f t="shared" si="0"/>
-        <v>9740</v>
-      </c>
-      <c r="F34" s="10">
-        <f t="shared" si="1"/>
-        <v>0.020219</v>
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
@@ -1913,416 +2555,344 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C35">
-        <v>5752</v>
+        <v>16</v>
       </c>
       <c r="D35">
-        <v>322</v>
+        <v>16</v>
       </c>
       <c r="E35">
-        <f t="shared" si="0"/>
-        <v>6074</v>
-      </c>
-      <c r="F35" s="10">
-        <f t="shared" si="1"/>
-        <v>0.01247</v>
+        <v>16</v>
+      </c>
+      <c r="F35">
+        <v>16</v>
+      </c>
+      <c r="G35">
+        <f>AVERAGE(B35:F35)</f>
+        <v>16</v>
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36">
-        <v>5</v>
-      </c>
-      <c r="C36">
-        <v>10773</v>
-      </c>
-      <c r="D36">
-        <v>728</v>
-      </c>
-      <c r="E36">
-        <f t="shared" si="0"/>
-        <v>11501</v>
-      </c>
-      <c r="F36" s="10">
-        <f t="shared" si="1"/>
-        <v>0.02373</v>
+      <c r="A36" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
     </row>
     <row r="37" spans="1:20">
-      <c r="A37" t="s">
-        <v>15</v>
+      <c r="A37" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C37">
-        <v>6556</v>
+        <v>5</v>
       </c>
       <c r="D37">
-        <v>270</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <f t="shared" si="0"/>
-        <v>6826</v>
-      </c>
-      <c r="F37" s="10">
-        <f t="shared" si="1"/>
-        <v>0.013922</v>
+        <v>5</v>
+      </c>
+      <c r="F37">
+        <v>5</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
     </row>
+    <row r="38" spans="1:20">
+      <c r="A38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
     <row r="39" spans="1:20">
       <c r="A39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G39" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>27</v>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B40">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2">
-        <f>B40/(B40+C40)</f>
-        <v>1</v>
-      </c>
-      <c r="F40" s="2">
-        <f t="shared" ref="F40:F49" si="2">B40/(B40+D40)</f>
-        <v>0.9375</v>
-      </c>
-      <c r="G40" s="5">
-        <f>2*E40*F40/(E40+F40)</f>
-        <v>0.967741935483871</v>
-      </c>
-      <c r="H40" s="2">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="E40">
+        <v>10</v>
+      </c>
+      <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <f>AVERAGE(B40:F40)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:20">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41">
-        <v>13</v>
-      </c>
-      <c r="C41">
-        <v>3</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41" s="2">
-        <f t="shared" ref="E41:E49" si="3">B41/(B41+C41)</f>
-        <v>0.8125</v>
-      </c>
-      <c r="F41" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G41" s="5">
-        <f t="shared" ref="G41:G49" si="4">2*E41*F41/(E41+F41)</f>
-        <v>0.896551724137931</v>
-      </c>
-      <c r="H41" s="2">
-        <v>0.2</v>
+      <c r="A41" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:20">
-      <c r="A42" t="s">
+      <c r="A42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42">
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <v>9</v>
+      </c>
+      <c r="D42">
         <v>8</v>
       </c>
-      <c r="B42">
-        <v>7</v>
-      </c>
-      <c r="C42">
-        <v>3</v>
-      </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42" s="2">
-        <f t="shared" si="3"/>
-        <v>0.7</v>
-      </c>
-      <c r="F42" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G42" s="5">
-        <f t="shared" si="4"/>
-        <v>0.823529411764706</v>
-      </c>
-      <c r="H42" s="2">
-        <v>0.3</v>
+      <c r="E42">
+        <v>9</v>
+      </c>
+      <c r="F42">
+        <v>8</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="6"/>
+        <v>8.6</v>
       </c>
     </row>
     <row r="43" spans="1:20">
-      <c r="A43" t="s">
-        <v>9</v>
+      <c r="A43" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B43">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
+      <c r="A44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="6"/>
         <v>1.4</v>
-      </c>
-      <c r="E43" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F43" s="2">
-        <f t="shared" si="2"/>
-        <v>0.86</v>
-      </c>
-      <c r="G43" s="5">
-        <f t="shared" si="4"/>
-        <v>0.924731182795699</v>
-      </c>
-      <c r="H43" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20">
-      <c r="A44" t="s">
-        <v>10</v>
-      </c>
-      <c r="B44">
-        <v>3</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
-      <c r="E44" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F44" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G44" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H44" s="2">
-        <v>0.6667</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+      <c r="C45">
+        <v>9</v>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+      <c r="E45">
+        <v>9</v>
+      </c>
+      <c r="F45">
+        <v>8</v>
+      </c>
+      <c r="G45">
+        <f>AVERAGE(B45:F45)</f>
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
+      <c r="A46" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
+      <c r="A47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+      <c r="F47">
+        <v>3</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
+      <c r="A48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <f>AVERAGE(B50:F50)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B45">
-        <v>6</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F45" s="2">
-        <f t="shared" si="2"/>
-        <v>0.857142857142857</v>
-      </c>
-      <c r="G45" s="5">
-        <f t="shared" si="4"/>
-        <v>0.923076923076923</v>
-      </c>
-      <c r="H45" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
-      <c r="A46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46">
-        <v>3</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
-      </c>
-      <c r="D46">
-        <v>0</v>
-      </c>
-      <c r="E46" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F46" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G46" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
-      <c r="A47" t="s">
-        <v>13</v>
-      </c>
-      <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>0</v>
-      </c>
-      <c r="E47" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F47" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G47" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="A48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B48">
-        <v>3</v>
-      </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
-      <c r="E48" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F48" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G48" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H48" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
-      </c>
-      <c r="D49">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="F49" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="G49" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H49" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="D50" s="9">
-        <f>AVERAGE(D40:D49)</f>
-        <v>0.34</v>
-      </c>
-      <c r="E50" s="5">
-        <f>AVERAGE(E40:E49)</f>
-        <v>0.95125</v>
-      </c>
-      <c r="F50" s="5">
-        <f>AVERAGE(F40:F49)</f>
-        <v>0.965464285714286</v>
-      </c>
-      <c r="G50" s="5">
-        <f>AVERAGE(G40:G49)</f>
-        <v>0.953563117725913</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2330,6 +2900,25 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>6</v>
+      </c>
+      <c r="D52">
+        <v>6</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="J52" s="2"/>
@@ -2338,26 +2927,26 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B53">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <f>AVERAGE(B53:F53)</f>
-        <v>15</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -2365,7 +2954,7 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -2383,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <f t="shared" ref="G54:G100" si="5">AVERAGE(B54:F54)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J54" s="2"/>
@@ -2391,40 +2980,62 @@
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="1" t="s">
-        <v>23</v>
+      <c r="A55" t="s">
+        <v>28</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G55">
-        <f t="shared" si="5"/>
-        <v>1</v>
+        <f>AVERAGE(B55:F55)</f>
+        <v>6</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
+      <c r="A56" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+      <c r="F57">
+        <v>3</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="2"/>
@@ -2432,26 +3043,26 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B58">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F58">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <f t="shared" si="5"/>
-        <v>13</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -2459,172 +3070,218 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <f t="shared" si="5"/>
-        <v>3</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="1" t="s">
-        <v>23</v>
+      <c r="A60" t="s">
+        <v>28</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G60">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(B60:F60)</f>
+        <v>3</v>
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12">
+      <c r="A61" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <f t="shared" si="6"/>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B63">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <f t="shared" si="5"/>
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <f t="shared" si="5"/>
-        <v>3</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="1" t="s">
-        <v>23</v>
+      <c r="A65" t="s">
+        <v>28</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(B65:F65)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <v>3</v>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="6"/>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B68">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <f t="shared" si="5"/>
-        <v>8.6</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -2642,66 +3299,90 @@
         <v>0</v>
       </c>
       <c r="G69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="1" t="s">
-        <v>23</v>
+      <c r="A70" t="s">
+        <v>28</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <f t="shared" si="5"/>
-        <v>1.4</v>
+        <f>AVERAGE(B70:F70)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <f t="shared" si="5"/>
-        <v>3</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -2719,417 +3400,32 @@
         <v>0</v>
       </c>
       <c r="G74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="1" t="s">
-        <v>23</v>
+      <c r="A75" t="s">
+        <v>28</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78">
-        <v>6</v>
-      </c>
-      <c r="C78">
-        <v>6</v>
-      </c>
-      <c r="D78">
-        <v>6</v>
-      </c>
-      <c r="E78">
-        <v>6</v>
-      </c>
-      <c r="F78">
-        <v>6</v>
-      </c>
-      <c r="G78">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B79">
-        <v>0</v>
-      </c>
-      <c r="C79">
-        <v>0</v>
-      </c>
-      <c r="D79">
-        <v>0</v>
-      </c>
-      <c r="E79">
-        <v>0</v>
-      </c>
-      <c r="F79">
-        <v>0</v>
-      </c>
-      <c r="G79">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B80">
-        <v>1</v>
-      </c>
-      <c r="C80">
-        <v>1</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-      <c r="E80">
-        <v>1</v>
-      </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-      <c r="G80">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B83">
-        <v>3</v>
-      </c>
-      <c r="C83">
-        <v>3</v>
-      </c>
-      <c r="D83">
-        <v>3</v>
-      </c>
-      <c r="E83">
-        <v>3</v>
-      </c>
-      <c r="F83">
-        <v>3</v>
-      </c>
-      <c r="G83">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B84">
-        <v>0</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="G84">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B85">
-        <v>0</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-      <c r="F85">
-        <v>0</v>
-      </c>
-      <c r="G85">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B88">
-        <v>2</v>
-      </c>
-      <c r="C88">
-        <v>2</v>
-      </c>
-      <c r="D88">
-        <v>2</v>
-      </c>
-      <c r="E88">
-        <v>2</v>
-      </c>
-      <c r="F88">
-        <v>2</v>
-      </c>
-      <c r="G88">
-        <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89">
-        <v>0</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89">
-        <v>0</v>
-      </c>
-      <c r="G89">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B90">
-        <v>0</v>
-      </c>
-      <c r="C90">
-        <v>0</v>
-      </c>
-      <c r="D90">
-        <v>0</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-      <c r="G90">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B93">
-        <v>3</v>
-      </c>
-      <c r="C93">
-        <v>3</v>
-      </c>
-      <c r="D93">
-        <v>3</v>
-      </c>
-      <c r="E93">
-        <v>3</v>
-      </c>
-      <c r="F93">
-        <v>3</v>
-      </c>
-      <c r="G93">
-        <f t="shared" si="5"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B94">
-        <v>0</v>
-      </c>
-      <c r="C94">
-        <v>0</v>
-      </c>
-      <c r="D94">
-        <v>0</v>
-      </c>
-      <c r="E94">
-        <v>0</v>
-      </c>
-      <c r="F94">
-        <v>0</v>
-      </c>
-      <c r="G94">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B95">
-        <v>0</v>
-      </c>
-      <c r="C95">
-        <v>0</v>
-      </c>
-      <c r="D95">
-        <v>0</v>
-      </c>
-      <c r="E95">
-        <v>0</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-      <c r="G95">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="C98">
-        <v>1</v>
-      </c>
-      <c r="D98">
-        <v>1</v>
-      </c>
-      <c r="E98">
-        <v>1</v>
-      </c>
-      <c r="F98">
-        <v>1</v>
-      </c>
-      <c r="G98">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99">
-        <v>0</v>
-      </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
-      <c r="D99">
-        <v>0</v>
-      </c>
-      <c r="E99">
-        <v>0</v>
-      </c>
-      <c r="F99">
-        <v>0</v>
-      </c>
-      <c r="G99">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B100">
-        <v>0</v>
-      </c>
-      <c r="C100">
-        <v>0</v>
-      </c>
-      <c r="D100">
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <v>0</v>
-      </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-      <c r="G100">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>AVERAGE(B75:F75)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3138,7 +3434,1458 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I75"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="33.1730769230769" customWidth="1"/>
+    <col min="2" max="2" width="12.4903846153846" customWidth="1"/>
+    <col min="3" max="3" width="12.9711538461538" customWidth="1"/>
+    <col min="4" max="4" width="14.2596153846154" customWidth="1"/>
+    <col min="5" max="5" width="13.2884615384615" customWidth="1"/>
+    <col min="6" max="6" width="14.2596153846154" customWidth="1"/>
+    <col min="7" max="7" width="12.8076923076923" customWidth="1"/>
+    <col min="8" max="8" width="11.6923076923077" customWidth="1"/>
+    <col min="9" max="9" width="15.2307692307692"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>62459</v>
+      </c>
+      <c r="D2">
+        <v>3630</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ref="E2:E10" si="0">C2+D2</f>
+        <v>66089</v>
+      </c>
+      <c r="F2" s="10">
+        <f>C2*(2.5/1000000)+D2*(15/1000000)</f>
+        <v>0.2105975</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>34</v>
+      </c>
+      <c r="C3">
+        <v>73035</v>
+      </c>
+      <c r="D3">
+        <v>3578</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>76613</v>
+      </c>
+      <c r="F3" s="10">
+        <f t="shared" ref="F3:F11" si="1">C3*(2.5/1000000)+D3*(15/1000000)</f>
+        <v>0.2362575</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>60542</v>
+      </c>
+      <c r="D4">
+        <v>2404</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>62946</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" si="1"/>
+        <v>0.187415</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>41866</v>
+      </c>
+      <c r="D5">
+        <v>2614</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>44480</v>
+      </c>
+      <c r="F5" s="10">
+        <f t="shared" si="1"/>
+        <v>0.143875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>18772</v>
+      </c>
+      <c r="D6">
+        <v>1540</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>20312</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="1"/>
+        <v>0.07003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>33341</v>
+      </c>
+      <c r="D7">
+        <v>1395</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>34736</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="1"/>
+        <v>0.1042775</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>8783</v>
+      </c>
+      <c r="D8">
+        <v>719</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>9502</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="1"/>
+        <v>0.0327425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>5588</v>
+      </c>
+      <c r="D9">
+        <v>294</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>5882</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="1"/>
+        <v>0.01838</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>10466</v>
+      </c>
+      <c r="D10">
+        <v>628</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>11094</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="1"/>
+        <v>0.035585</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>6283</v>
+      </c>
+      <c r="D11">
+        <v>229</v>
+      </c>
+      <c r="E11">
+        <f>C11+D11</f>
+        <v>6512</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="1"/>
+        <v>0.0191425</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="11">
+        <f>E27</f>
+        <v>15</v>
+      </c>
+      <c r="C14" s="12">
+        <f>E28</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="12">
+        <f>E29</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <f>B14/(B14+C14)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <f>B14/(B14+D14)</f>
+        <v>0.9375</v>
+      </c>
+      <c r="G14" s="5">
+        <f>2*E14*F14/(E14+F14)</f>
+        <v>0.967741935483871</v>
+      </c>
+      <c r="H14" s="2">
+        <f>(I14-B14)/I14</f>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f>E30</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="11">
+        <f>E32</f>
+        <v>15</v>
+      </c>
+      <c r="C15" s="12">
+        <f>E33</f>
+        <v>1</v>
+      </c>
+      <c r="D15" s="12">
+        <f>E34</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" ref="E15:E23" si="2">B15/(B15+C15)</f>
+        <v>0.9375</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" ref="F15:F23" si="3">B15/(B15+D15)</f>
+        <v>0.957446808510638</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" ref="G15:G23" si="4">2*E15*F15/(E15+F15)</f>
+        <v>0.947368421052632</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" ref="H15:H23" si="5">(I15-B15)/I15</f>
+        <v>0.1</v>
+      </c>
+      <c r="I15" s="12">
+        <f>E35</f>
+        <v>16.6666666666667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="11">
+        <f>E37</f>
+        <v>3</v>
+      </c>
+      <c r="C16" s="12">
+        <f>E38</f>
+        <v>5</v>
+      </c>
+      <c r="D16" s="12">
+        <f>E39</f>
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.375</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="3"/>
+        <v>0.6</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="4"/>
+        <v>0.461538461538462</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="5"/>
+        <v>0.625</v>
+      </c>
+      <c r="I16" s="12">
+        <f>E40</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="11">
+        <f>E42</f>
+        <v>10</v>
+      </c>
+      <c r="C17" s="12">
+        <f>E43</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="12">
+        <f>E44</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="12">
+        <f>E45</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="11">
+        <f>E47</f>
+        <v>3</v>
+      </c>
+      <c r="C18" s="12">
+        <f>E48</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="12">
+        <f>E49</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="I18" s="12">
+        <f>E50</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="11">
+        <f>E52</f>
+        <v>5</v>
+      </c>
+      <c r="C19" s="12">
+        <f>E53</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="12">
+        <f>E54</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="2"/>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="4"/>
+        <v>0.909090909090909</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="5"/>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I19" s="12">
+        <f>E55</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="11">
+        <f>E57</f>
+        <v>3</v>
+      </c>
+      <c r="C20" s="12">
+        <f>E58</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="12">
+        <f>E59</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="12">
+        <f>E60</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="11">
+        <f>E62</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="12">
+        <f>E63</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="12">
+        <f>E59</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="12">
+        <f>E65</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="11">
+        <f>E67</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="12">
+        <f>E68</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="12">
+        <f>E64</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="12">
+        <f>E70</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="11">
+        <f>E72</f>
+        <v>1</v>
+      </c>
+      <c r="C23" s="12">
+        <f>E73</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="12">
+        <f>E69</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="12">
+        <f>E75</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="D24" s="9"/>
+      <c r="E24" s="5">
+        <f>AVERAGE(E14:E23)</f>
+        <v>0.914583333333333</v>
+      </c>
+      <c r="F24" s="5">
+        <f>AVERAGE(F14:F23)</f>
+        <v>0.949494680851064</v>
+      </c>
+      <c r="G24" s="5">
+        <f>AVERAGE(G14:G23)</f>
+        <v>0.928573972716587</v>
+      </c>
+      <c r="H24" s="5">
+        <f>AVERAGE(H14:H23)</f>
+        <v>0.129166666666667</v>
+      </c>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>15</v>
+      </c>
+      <c r="E27">
+        <f>AVERAGE(B27:D27)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <f t="shared" ref="E28:E41" si="6">AVERAGE(B28:D28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
+      <c r="C30">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <f>AVERAGE(B30:D30)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <v>15</v>
+      </c>
+      <c r="D32">
+        <v>15</v>
+      </c>
+      <c r="E32" s="12">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" s="12">
+        <f t="shared" si="6"/>
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35">
+        <v>15</v>
+      </c>
+      <c r="C35">
+        <v>19</v>
+      </c>
+      <c r="D35">
+        <v>16</v>
+      </c>
+      <c r="E35" s="12">
+        <f>AVERAGE(B35:D35)</f>
+        <v>16.6666666666667</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+      <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
+        <f>AVERAGE(B40:D40)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42">
+        <v>10</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <f>AVERAGE(B42:D42)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <f t="shared" ref="E43:E74" si="7">AVERAGE(B43:D43)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45">
+        <v>10</v>
+      </c>
+      <c r="C45">
+        <v>10</v>
+      </c>
+      <c r="D45">
+        <v>10</v>
+      </c>
+      <c r="E45">
+        <f>AVERAGE(B45:D45)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50">
+        <f>AVERAGE(B50:D50)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+      <c r="C52">
+        <v>5</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>6</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+      <c r="E55">
+        <f>AVERAGE(B55:D55)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65">
+        <f>AVERAGE(B65:D65)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70">
+        <v>3</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70">
+        <f>AVERAGE(B70:D70)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75">
+        <f>AVERAGE(B75:D75)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H12"/>
@@ -3171,7 +4918,7 @@
         <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3488,7 +5235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L187"/>
@@ -3509,25 +5256,25 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3836,10 +5583,10 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="3"/>
@@ -4236,10 +5983,10 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -4634,10 +6381,10 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -5032,10 +6779,10 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -5430,10 +7177,10 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -5828,10 +7575,10 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -6229,10 +7976,10 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -6633,10 +8380,10 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C107" s="1"/>
       <c r="L107" s="4"/>
@@ -7036,10 +8783,10 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L119" s="4"/>
     </row>
@@ -7435,30 +9182,30 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135" spans="1:12">
       <c r="A135" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -7701,30 +9448,30 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -7959,10 +9706,10 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -8126,10 +9873,10 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -8290,10 +10037,10 @@
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I177" s="3"/>
     </row>
@@ -8474,7 +10221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G19"/>
@@ -8489,25 +10236,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8755,7 +10502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G11"/>
@@ -8771,25 +10518,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -9028,7 +10775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G11"/>
@@ -9044,25 +10791,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:7">

--- a/data/results.xlsx
+++ b/data/results.xlsx
@@ -4,17 +4,18 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26300" windowHeight="11780" tabRatio="882" activeTab="2"/>
+    <workbookView windowWidth="26300" windowHeight="11780" tabRatio="882" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="dataset" sheetId="8" r:id="rId1"/>
     <sheet name="DeepSeek Generate" sheetId="1" r:id="rId2"/>
     <sheet name="ChatGPT Generate" sheetId="7" r:id="rId3"/>
-    <sheet name="Static Analysis (reproduction)" sheetId="2" r:id="rId4"/>
-    <sheet name="automatic testing" sheetId="3" r:id="rId5"/>
-    <sheet name="LMT vs RT" sheetId="4" r:id="rId6"/>
-    <sheet name="LMT vs SAMT" sheetId="5" r:id="rId7"/>
-    <sheet name="LMT vs SAMT2" sheetId="6" r:id="rId8"/>
+    <sheet name="Claude Code Generate" sheetId="9" r:id="rId4"/>
+    <sheet name="Static Analysis (reproduction)" sheetId="2" r:id="rId5"/>
+    <sheet name="automatic testing" sheetId="3" r:id="rId6"/>
+    <sheet name="LMT vs RT" sheetId="4" r:id="rId7"/>
+    <sheet name="LMT vs SAMT" sheetId="5" r:id="rId8"/>
+    <sheet name="LMT vs SAMT2" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="52">
   <si>
     <t>HarmonyOS App</t>
   </si>
@@ -117,10 +118,10 @@
     <t>F1</t>
   </si>
   <si>
-    <t>HER</t>
+    <t>TE</t>
   </si>
   <si>
-    <t>AE</t>
+    <t>HER</t>
   </si>
   <si>
     <t>FNR</t>
@@ -202,10 +203,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;US$&quot;#,##0.00_);[Red]\(&quot;US$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
-    <numFmt numFmtId="179" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
-    <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;US$&quot;#,##0.00_);[Red]\(&quot;US$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="180" formatCode="&quot;￥&quot;#,##0.00_);[Red]\(&quot;￥&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -818,7 +819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -849,10 +850,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -861,7 +865,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1389,7 +1393,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="36.0576923076923" customWidth="1"/>
@@ -1613,6 +1617,28 @@
       </c>
       <c r="F11">
         <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12">
+        <f>SUM(B2:B11)</f>
+        <v>392</v>
+      </c>
+      <c r="C12">
+        <f>SUM(C2:C11)</f>
+        <v>44819</v>
+      </c>
+      <c r="D12">
+        <f>SUM(D2:D11)</f>
+        <v>4953</v>
+      </c>
+      <c r="E12">
+        <f>SUM(E2:E11)</f>
+        <v>2012</v>
+      </c>
+      <c r="F12">
+        <f>SUM(F2:F11)</f>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1669,21 +1695,21 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2">
-        <v>65205</v>
+        <v>77295</v>
       </c>
       <c r="D2">
-        <v>3979</v>
+        <v>4627</v>
       </c>
       <c r="E2">
         <f t="shared" ref="E2:E11" si="0">C2+D2</f>
-        <v>69184</v>
-      </c>
-      <c r="F2" s="13">
+        <v>81922</v>
+      </c>
+      <c r="F2" s="15">
         <f>C2*(2/1000000)+D2*(3/1000000)</f>
-        <v>0.142347</v>
+        <v>0.168471</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1706,7 +1732,7 @@
         <f t="shared" si="0"/>
         <v>80457</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="15">
         <f t="shared" ref="F3:F11" si="1">C3*(2/1000000)+D3*(3/1000000)</f>
         <v>0.165559</v>
       </c>
@@ -1719,21 +1745,21 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C4">
-        <v>63422</v>
+        <v>85374</v>
       </c>
       <c r="D4">
-        <v>3006</v>
+        <v>4408</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>66428</v>
-      </c>
-      <c r="F4" s="13">
+        <v>89782</v>
+      </c>
+      <c r="F4" s="15">
         <f t="shared" si="1"/>
-        <v>0.135862</v>
+        <v>0.183972</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1744,21 +1770,21 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>42969</v>
+        <v>66486</v>
       </c>
       <c r="D5">
-        <v>2566</v>
+        <v>3651</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>45535</v>
-      </c>
-      <c r="F5" s="13">
+        <v>70137</v>
+      </c>
+      <c r="F5" s="15">
         <f t="shared" si="1"/>
-        <v>0.093636</v>
+        <v>0.143925</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1772,18 +1798,18 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>15212</v>
+        <v>17909</v>
       </c>
       <c r="D6">
-        <v>1207</v>
+        <v>1378</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>16419</v>
-      </c>
-      <c r="F6" s="13">
+        <v>19287</v>
+      </c>
+      <c r="F6" s="15">
         <f t="shared" si="1"/>
-        <v>0.034045</v>
+        <v>0.039952</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1794,21 +1820,21 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>33269</v>
+        <v>41916</v>
       </c>
       <c r="D7">
-        <v>1673</v>
+        <v>2520</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>34942</v>
-      </c>
-      <c r="F7" s="13">
+        <v>44436</v>
+      </c>
+      <c r="F7" s="15">
         <f t="shared" si="1"/>
-        <v>0.071557</v>
+        <v>0.091392</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1822,18 +1848,18 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>9001</v>
+        <v>10443</v>
       </c>
       <c r="D8">
-        <v>739</v>
+        <v>908</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>9740</v>
-      </c>
-      <c r="F8" s="13">
+        <v>11351</v>
+      </c>
+      <c r="F8" s="15">
         <f t="shared" si="1"/>
-        <v>0.020219</v>
+        <v>0.02361</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="2"/>
@@ -1847,18 +1873,18 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>5752</v>
+        <v>6600</v>
       </c>
       <c r="D9">
-        <v>322</v>
+        <v>384</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>6074</v>
-      </c>
-      <c r="F9" s="13">
+        <v>6984</v>
+      </c>
+      <c r="F9" s="15">
         <f t="shared" si="1"/>
-        <v>0.01247</v>
+        <v>0.014352</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="2"/>
@@ -1872,18 +1898,18 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>10773</v>
+        <v>12065</v>
       </c>
       <c r="D10">
-        <v>728</v>
+        <v>809</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>11501</v>
-      </c>
-      <c r="F10" s="13">
+        <v>12874</v>
+      </c>
+      <c r="F10" s="15">
         <f t="shared" si="1"/>
-        <v>0.02373</v>
+        <v>0.026557</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="2"/>
@@ -1897,18 +1923,18 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>6556</v>
+        <v>7469</v>
       </c>
       <c r="D11">
         <v>270</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>6826</v>
-      </c>
-      <c r="F11" s="13">
+        <v>7739</v>
+      </c>
+      <c r="F11" s="15">
         <f t="shared" si="1"/>
-        <v>0.013922</v>
+        <v>0.015748</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="2"/>
@@ -1942,7 +1968,7 @@
       <c r="H13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1950,13 +1976,16 @@
       <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="10">
+        <f>E27</f>
         <v>15</v>
       </c>
-      <c r="C14" s="12">
-        <v>0</v>
-      </c>
-      <c r="D14" s="12">
+      <c r="C14" s="11">
+        <f>E28</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="11">
+        <f>E29</f>
         <v>1</v>
       </c>
       <c r="E14" s="2">
@@ -1971,25 +2000,29 @@
         <f>2*E14*F14/(E14+F14)</f>
         <v>0.967741935483871</v>
       </c>
-      <c r="H14" s="2">
-        <f>(I14-B14)/I14</f>
-        <v>0</v>
-      </c>
-      <c r="I14">
+      <c r="H14" s="11">
+        <f>E30</f>
         <v>15</v>
+      </c>
+      <c r="I14" s="5">
+        <f>(H14-B14)/H14</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="10">
+        <f>E32</f>
         <v>13</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
+        <f>E33</f>
         <v>3</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
+        <f>E34</f>
         <v>0</v>
       </c>
       <c r="E15" s="2">
@@ -2004,12 +2037,13 @@
         <f t="shared" ref="G15:G23" si="4">2*E15*F15/(E15+F15)</f>
         <v>0.896551724137931</v>
       </c>
-      <c r="H15" s="2">
-        <f t="shared" ref="H15:H23" si="5">(I15-B15)/I15</f>
-        <v>0.1875</v>
-      </c>
-      <c r="I15" s="1">
-        <v>16</v>
+      <c r="H15" s="11">
+        <f>E35</f>
+        <v>17</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" ref="I15:I23" si="5">(H15-B15)/H15</f>
+        <v>0.235294117647059</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -2023,18 +2057,21 @@
       <c r="A16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="12">
-        <v>5</v>
-      </c>
-      <c r="C16" s="12">
-        <v>5</v>
-      </c>
-      <c r="D16" s="12">
+      <c r="B16" s="10">
+        <f>E37</f>
+        <v>6</v>
+      </c>
+      <c r="C16" s="11">
+        <f>E38</f>
+        <v>4</v>
+      </c>
+      <c r="D16" s="11">
+        <f>E39</f>
         <v>0</v>
       </c>
       <c r="E16" s="2">
         <f t="shared" si="2"/>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="3"/>
@@ -2042,14 +2079,15 @@
       </c>
       <c r="G16" s="5">
         <f t="shared" si="4"/>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="H16" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="H16" s="11">
+        <f>E40</f>
+        <v>10</v>
+      </c>
+      <c r="I16" s="5">
         <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="I16">
-        <v>10</v>
+        <v>0.4</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2059,14 +2097,17 @@
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="12">
-        <v>8.6</v>
-      </c>
-      <c r="C17" s="12">
-        <v>0</v>
-      </c>
-      <c r="D17" s="12">
-        <v>1.4</v>
+      <c r="B17" s="10">
+        <f>E42</f>
+        <v>10</v>
+      </c>
+      <c r="C17" s="11">
+        <f>E43</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="11">
+        <f>E44</f>
+        <v>0</v>
       </c>
       <c r="E17" s="2">
         <f t="shared" si="2"/>
@@ -2074,18 +2115,19 @@
       </c>
       <c r="F17" s="2">
         <f t="shared" si="3"/>
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="4"/>
-        <v>0.924731182795699</v>
-      </c>
-      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11">
+        <f>E45</f>
+        <v>10</v>
+      </c>
+      <c r="I17" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
-      </c>
-      <c r="I17">
-        <v>8.6</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2095,13 +2137,16 @@
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
+        <f>E47</f>
         <v>3</v>
       </c>
-      <c r="C18" s="12">
-        <v>0</v>
-      </c>
-      <c r="D18" s="12">
+      <c r="C18" s="11">
+        <f>E48</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="11">
+        <f>E49</f>
         <v>0</v>
       </c>
       <c r="E18" s="2">
@@ -2116,12 +2161,13 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="11">
+        <f>E50</f>
+        <v>5</v>
+      </c>
+      <c r="I18" s="5">
         <f t="shared" si="5"/>
         <v>0.4</v>
-      </c>
-      <c r="I18">
-        <v>5</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -2131,33 +2177,37 @@
       <c r="A19" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="12">
-        <v>6</v>
-      </c>
-      <c r="C19" s="12">
-        <v>0</v>
-      </c>
-      <c r="D19" s="12">
-        <v>0</v>
+      <c r="B19" s="10">
+        <f>E52</f>
+        <v>4.33333333333333</v>
+      </c>
+      <c r="C19" s="11">
+        <f>E53</f>
+        <v>1.66666666666667</v>
+      </c>
+      <c r="D19" s="11">
+        <f>E54</f>
+        <v>1</v>
       </c>
       <c r="E19" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.722222222222222</v>
       </c>
       <c r="F19" s="2">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.8125</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
+        <v>0.764705882352941</v>
+      </c>
+      <c r="H19" s="11">
+        <f>E55</f>
+        <v>6</v>
+      </c>
+      <c r="I19" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>6</v>
+        <v>0.277777777777778</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2167,13 +2217,16 @@
       <c r="A20" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="10">
+        <f>E57</f>
         <v>3</v>
       </c>
-      <c r="C20" s="12">
-        <v>0</v>
-      </c>
-      <c r="D20" s="12">
+      <c r="C20" s="11">
+        <f>E58</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="11">
+        <f>E59</f>
         <v>0</v>
       </c>
       <c r="E20" s="2">
@@ -2188,12 +2241,13 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="11">
+        <f>E60</f>
+        <v>3</v>
+      </c>
+      <c r="I20" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
-      </c>
-      <c r="I20">
-        <v>3</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2203,13 +2257,16 @@
       <c r="A21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="10">
+        <f>E62</f>
         <v>2</v>
       </c>
-      <c r="C21" s="12">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12">
+      <c r="C21" s="11">
+        <f>E63</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="11">
+        <f>E59</f>
         <v>0</v>
       </c>
       <c r="E21" s="2">
@@ -2224,12 +2281,13 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="11">
+        <f>E65</f>
+        <v>2</v>
+      </c>
+      <c r="I21" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
-      </c>
-      <c r="I21">
-        <v>2</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="2"/>
@@ -2239,13 +2297,16 @@
       <c r="A22" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="10">
+        <f>E67</f>
         <v>3</v>
       </c>
-      <c r="C22" s="12">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12">
+      <c r="C22" s="11">
+        <f>E68</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="11">
+        <f>E64</f>
         <v>0</v>
       </c>
       <c r="E22" s="2">
@@ -2260,12 +2321,13 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="11">
+        <f>E70</f>
+        <v>3</v>
+      </c>
+      <c r="I22" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
-      </c>
-      <c r="I22">
-        <v>3</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -2275,13 +2337,16 @@
       <c r="A23" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="12">
-        <v>1</v>
-      </c>
-      <c r="C23" s="12">
-        <v>0</v>
-      </c>
-      <c r="D23" s="12">
+      <c r="B23" s="10">
+        <f>E72</f>
+        <v>1</v>
+      </c>
+      <c r="C23" s="11">
+        <f>E73</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="11">
+        <f>E69</f>
         <v>0</v>
       </c>
       <c r="E23" s="2">
@@ -2296,36 +2361,50 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="11">
+        <f>E75</f>
+        <v>1</v>
+      </c>
+      <c r="I23" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:24">
-      <c r="B24" s="14"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="12">
+        <f>AVERAGE(B14:B23)</f>
+        <v>6.03333333333333</v>
+      </c>
+      <c r="C24" s="12">
+        <f>AVERAGE(C14:C23)</f>
+        <v>0.866666666666667</v>
+      </c>
+      <c r="D24" s="12">
+        <f>AVERAGE(D14:D23)</f>
+        <v>0.2</v>
+      </c>
       <c r="E24" s="5">
-        <f>AVERAGE(E14:E23)</f>
-        <v>0.93125</v>
+        <f t="shared" ref="E24:I24" si="6">AVERAGE(E14:E23)</f>
+        <v>0.913472222222222</v>
       </c>
       <c r="F24" s="5">
-        <f>AVERAGE(F14:F23)</f>
-        <v>0.97975</v>
+        <f t="shared" si="6"/>
+        <v>0.975</v>
       </c>
       <c r="G24" s="5">
-        <f>AVERAGE(G14:G23)</f>
-        <v>0.945569150908417</v>
-      </c>
-      <c r="H24" s="5">
-        <f>AVERAGE(H14:H23)</f>
-        <v>0.10875</v>
+        <f t="shared" si="6"/>
+        <v>0.937899954197474</v>
+      </c>
+      <c r="H24" s="12">
+        <f t="shared" si="6"/>
+        <v>7.2</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="6"/>
+        <v>0.131307189542484</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -2356,14 +2435,8 @@
       <c r="D27">
         <v>15</v>
       </c>
-      <c r="E27">
-        <v>15</v>
-      </c>
-      <c r="F27">
-        <v>15</v>
-      </c>
-      <c r="G27">
-        <f>AVERAGE(B27:F27)</f>
+      <c r="E27" s="11">
+        <f>AVERAGE(B27:D27)</f>
         <v>15</v>
       </c>
       <c r="I27" s="1"/>
@@ -2396,14 +2469,8 @@
       <c r="D28">
         <v>0</v>
       </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <f t="shared" ref="G28:G74" si="6">AVERAGE(B28:F28)</f>
+      <c r="E28" s="11">
+        <f>AVERAGE(B28:D28)</f>
         <v>0</v>
       </c>
       <c r="R28" s="2"/>
@@ -2423,14 +2490,8 @@
       <c r="D29">
         <v>1</v>
       </c>
-      <c r="E29">
-        <v>1</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="6"/>
+      <c r="E29" s="11">
+        <f>AVERAGE(B29:D29)</f>
         <v>1</v>
       </c>
       <c r="R29" s="2"/>
@@ -2439,7 +2500,7 @@
     </row>
     <row r="30" spans="1:24">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>15</v>
@@ -2450,14 +2511,8 @@
       <c r="D30">
         <v>15</v>
       </c>
-      <c r="E30">
-        <v>15</v>
-      </c>
-      <c r="F30">
-        <v>15</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="6"/>
+      <c r="E30" s="11">
+        <f>AVERAGE(B30:D30)</f>
         <v>15</v>
       </c>
       <c r="R30" s="2"/>
@@ -2468,6 +2523,7 @@
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="E31" s="11"/>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
@@ -2485,14 +2541,8 @@
       <c r="D32">
         <v>13</v>
       </c>
-      <c r="E32">
-        <v>13</v>
-      </c>
-      <c r="F32">
-        <v>13</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="6"/>
+      <c r="E32" s="11">
+        <f>AVERAGE(B32:D32)</f>
         <v>13</v>
       </c>
       <c r="R32" s="2"/>
@@ -2512,14 +2562,8 @@
       <c r="D33">
         <v>3</v>
       </c>
-      <c r="E33">
-        <v>3</v>
-      </c>
-      <c r="F33">
-        <v>3</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="6"/>
+      <c r="E33" s="11">
+        <f>AVERAGE(B33:D33)</f>
         <v>3</v>
       </c>
       <c r="R33" s="5"/>
@@ -2539,14 +2583,8 @@
       <c r="D34">
         <v>0</v>
       </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="6"/>
+      <c r="E34" s="11">
+        <f>AVERAGE(B34:D34)</f>
         <v>0</v>
       </c>
       <c r="R34" s="2"/>
@@ -2555,26 +2593,20 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35">
         <v>16</v>
       </c>
       <c r="C35">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D35">
-        <v>16</v>
-      </c>
-      <c r="E35">
-        <v>16</v>
-      </c>
-      <c r="F35">
-        <v>16</v>
-      </c>
-      <c r="G35">
-        <f>AVERAGE(B35:F35)</f>
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="E35" s="11">
+        <f>AVERAGE(B35:D35)</f>
+        <v>17</v>
       </c>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
@@ -2584,6 +2616,7 @@
       <c r="A36" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="E36" s="11"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
@@ -2593,23 +2626,17 @@
         <v>21</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>5</v>
-      </c>
-      <c r="E37">
-        <v>5</v>
-      </c>
-      <c r="F37">
-        <v>5</v>
-      </c>
-      <c r="G37">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="E37" s="11">
+        <f>AVERAGE(B37:D37)</f>
+        <v>6</v>
       </c>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
@@ -2620,23 +2647,17 @@
         <v>22</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>5</v>
-      </c>
-      <c r="E38">
-        <v>5</v>
-      </c>
-      <c r="F38">
-        <v>5</v>
-      </c>
-      <c r="G38">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="E38" s="11">
+        <f>AVERAGE(B38:D38)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:20">
@@ -2652,20 +2673,14 @@
       <c r="D39">
         <v>0</v>
       </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <f t="shared" si="6"/>
+      <c r="E39" s="11">
+        <f>AVERAGE(B39:D39)</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40">
         <v>10</v>
@@ -2676,14 +2691,8 @@
       <c r="D40">
         <v>10</v>
       </c>
-      <c r="E40">
-        <v>10</v>
-      </c>
-      <c r="F40">
-        <v>10</v>
-      </c>
-      <c r="G40">
-        <f>AVERAGE(B40:F40)</f>
+      <c r="E40" s="11">
+        <f>AVERAGE(B40:D40)</f>
         <v>10</v>
       </c>
     </row>
@@ -2697,23 +2706,17 @@
         <v>21</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D42">
-        <v>8</v>
-      </c>
-      <c r="E42">
-        <v>9</v>
-      </c>
-      <c r="F42">
-        <v>8</v>
-      </c>
-      <c r="G42">
-        <f t="shared" si="6"/>
-        <v>8.6</v>
+        <v>10</v>
+      </c>
+      <c r="E42" s="11">
+        <f>AVERAGE(B42:D42)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:20">
@@ -2729,14 +2732,8 @@
       <c r="D43">
         <v>0</v>
       </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-      <c r="G43">
-        <f t="shared" si="6"/>
+      <c r="E43" s="11">
+        <f>AVERAGE(B43:D43)</f>
         <v>0</v>
       </c>
     </row>
@@ -2745,53 +2742,42 @@
         <v>23</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>2</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44">
-        <f t="shared" si="6"/>
-        <v>1.4</v>
+        <v>0</v>
+      </c>
+      <c r="E44" s="11">
+        <f>AVERAGE(B44:D44)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45">
-        <v>8</v>
-      </c>
-      <c r="E45">
-        <v>9</v>
-      </c>
-      <c r="F45">
-        <v>8</v>
-      </c>
-      <c r="G45">
-        <f>AVERAGE(B45:F45)</f>
-        <v>8.6</v>
+        <v>10</v>
+      </c>
+      <c r="E45" s="11">
+        <f>AVERAGE(B45:D45)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" s="1" t="s">
@@ -2806,14 +2792,8 @@
       <c r="D47">
         <v>3</v>
       </c>
-      <c r="E47">
-        <v>3</v>
-      </c>
-      <c r="F47">
-        <v>3</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="6"/>
+      <c r="E47" s="11">
+        <f t="shared" ref="E46:E75" si="7">AVERAGE(B47:D47)</f>
         <v>3</v>
       </c>
     </row>
@@ -2830,14 +2810,8 @@
       <c r="D48">
         <v>0</v>
       </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="6"/>
+      <c r="E48" s="11">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2854,20 +2828,14 @@
       <c r="D49">
         <v>0</v>
       </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="6"/>
+      <c r="E49" s="11">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B50">
         <v>5</v>
@@ -2878,14 +2846,8 @@
       <c r="D50">
         <v>5</v>
       </c>
-      <c r="E50">
-        <v>5</v>
-      </c>
-      <c r="F50">
-        <v>5</v>
-      </c>
-      <c r="G50">
-        <f>AVERAGE(B50:F50)</f>
+      <c r="E50" s="11">
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -2893,6 +2855,7 @@
       <c r="A51" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="E51" s="11"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2903,23 +2866,17 @@
         <v>21</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52">
-        <v>6</v>
-      </c>
-      <c r="E52">
-        <v>6</v>
-      </c>
-      <c r="F52">
-        <v>6</v>
-      </c>
-      <c r="G52">
-        <f t="shared" si="6"/>
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="E52" s="11">
+        <f t="shared" si="7"/>
+        <v>4.33333333333333</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -2930,23 +2887,17 @@
         <v>22</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53">
-        <v>0</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E53" s="11">
+        <f t="shared" si="7"/>
+        <v>1.66666666666667</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -2957,23 +2908,17 @@
         <v>23</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-      <c r="G54">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E54" s="11">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -2981,7 +2926,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B55">
         <v>6</v>
@@ -2992,14 +2937,8 @@
       <c r="D55">
         <v>6</v>
       </c>
-      <c r="E55">
-        <v>6</v>
-      </c>
-      <c r="F55">
-        <v>6</v>
-      </c>
-      <c r="G55">
-        <f>AVERAGE(B55:F55)</f>
+      <c r="E55" s="11">
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="J55" s="2"/>
@@ -3010,6 +2949,7 @@
       <c r="A56" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="E56" s="11"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
@@ -3027,14 +2967,8 @@
       <c r="D57">
         <v>3</v>
       </c>
-      <c r="E57">
-        <v>3</v>
-      </c>
-      <c r="F57">
-        <v>3</v>
-      </c>
-      <c r="G57">
-        <f t="shared" si="6"/>
+      <c r="E57" s="11">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="J57" s="5"/>
@@ -3054,14 +2988,8 @@
       <c r="D58">
         <v>0</v>
       </c>
-      <c r="E58">
-        <v>0</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <f t="shared" si="6"/>
+      <c r="E58" s="11">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J58" s="2"/>
@@ -3081,14 +3009,8 @@
       <c r="D59">
         <v>0</v>
       </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>0</v>
-      </c>
-      <c r="G59">
-        <f t="shared" si="6"/>
+      <c r="E59" s="11">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="J59" s="2"/>
@@ -3097,7 +3019,7 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B60">
         <v>3</v>
@@ -3108,14 +3030,8 @@
       <c r="D60">
         <v>3</v>
       </c>
-      <c r="E60">
-        <v>3</v>
-      </c>
-      <c r="F60">
-        <v>3</v>
-      </c>
-      <c r="G60">
-        <f>AVERAGE(B60:F60)</f>
+      <c r="E60" s="11">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="J60" s="2"/>
@@ -3126,6 +3042,7 @@
       <c r="A61" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="E61" s="11"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
@@ -3143,14 +3060,8 @@
       <c r="D62">
         <v>2</v>
       </c>
-      <c r="E62">
-        <v>2</v>
-      </c>
-      <c r="F62">
-        <v>2</v>
-      </c>
-      <c r="G62">
-        <f t="shared" si="6"/>
+      <c r="E62" s="11">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -3167,14 +3078,8 @@
       <c r="D63">
         <v>0</v>
       </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>0</v>
-      </c>
-      <c r="G63">
-        <f t="shared" si="6"/>
+      <c r="E63" s="11">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3191,20 +3096,14 @@
       <c r="D64">
         <v>0</v>
       </c>
-      <c r="E64">
-        <v>0</v>
-      </c>
-      <c r="F64">
-        <v>0</v>
-      </c>
-      <c r="G64">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+      <c r="E64" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -3215,23 +3114,18 @@
       <c r="D65">
         <v>2</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="11">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="F65">
-        <v>2</v>
-      </c>
-      <c r="G65">
-        <f>AVERAGE(B65:F65)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="E66" s="11"/>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
         <v>21</v>
       </c>
@@ -3244,18 +3138,12 @@
       <c r="D67">
         <v>3</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="11">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="F67">
-        <v>3</v>
-      </c>
-      <c r="G67">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" s="1" t="s">
         <v>22</v>
       </c>
@@ -3268,18 +3156,12 @@
       <c r="D68">
         <v>0</v>
       </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <v>0</v>
-      </c>
-      <c r="G68">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="E68" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" s="1" t="s">
         <v>23</v>
       </c>
@@ -3292,20 +3174,14 @@
       <c r="D69">
         <v>0</v>
       </c>
-      <c r="E69">
-        <v>0</v>
-      </c>
-      <c r="F69">
-        <v>0</v>
-      </c>
-      <c r="G69">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="E69" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B70">
         <v>3</v>
@@ -3316,23 +3192,18 @@
       <c r="D70">
         <v>3</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="11">
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
-      <c r="F70">
-        <v>3</v>
-      </c>
-      <c r="G70">
-        <f>AVERAGE(B70:F70)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="E71" s="11"/>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" s="1" t="s">
         <v>21</v>
       </c>
@@ -3345,18 +3216,12 @@
       <c r="D72">
         <v>1</v>
       </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="E72" s="11">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" s="1" t="s">
         <v>22</v>
       </c>
@@ -3369,18 +3234,12 @@
       <c r="D73">
         <v>0</v>
       </c>
-      <c r="E73">
-        <v>0</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="E73" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" s="1" t="s">
         <v>23</v>
       </c>
@@ -3393,20 +3252,14 @@
       <c r="D74">
         <v>0</v>
       </c>
-      <c r="E74">
-        <v>0</v>
-      </c>
-      <c r="F74">
-        <v>0</v>
-      </c>
-      <c r="G74">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="E74" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -3417,14 +3270,8 @@
       <c r="D75">
         <v>1</v>
       </c>
-      <c r="E75">
-        <v>1</v>
-      </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75">
-        <f>AVERAGE(B75:F75)</f>
+      <c r="E75" s="11">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -3479,18 +3326,18 @@
         <v>33</v>
       </c>
       <c r="C2">
-        <v>62459</v>
+        <v>71998</v>
       </c>
       <c r="D2">
-        <v>3630</v>
+        <v>4615</v>
       </c>
       <c r="E2">
-        <f t="shared" ref="E2:E10" si="0">C2+D2</f>
-        <v>66089</v>
-      </c>
-      <c r="F2" s="10">
+        <f t="shared" ref="E2:E11" si="0">C2+D2</f>
+        <v>76613</v>
+      </c>
+      <c r="F2" s="14">
         <f>C2*(2.5/1000000)+D2*(15/1000000)</f>
-        <v>0.2105975</v>
+        <v>0.24922</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3510,7 +3357,7 @@
         <f t="shared" si="0"/>
         <v>76613</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="14">
         <f t="shared" ref="F3:F11" si="1">C3*(2.5/1000000)+D3*(15/1000000)</f>
         <v>0.2362575</v>
       </c>
@@ -3520,21 +3367,21 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C4">
-        <v>60542</v>
+        <v>78130</v>
       </c>
       <c r="D4">
-        <v>2404</v>
+        <v>5641</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>62946</v>
-      </c>
-      <c r="F4" s="10">
+        <v>83771</v>
+      </c>
+      <c r="F4" s="14">
         <f t="shared" si="1"/>
-        <v>0.187415</v>
+        <v>0.27994</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3542,21 +3389,21 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>41866</v>
+        <v>63992</v>
       </c>
       <c r="D5">
-        <v>2614</v>
+        <v>3546</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>44480</v>
-      </c>
-      <c r="F5" s="10">
+        <v>67538</v>
+      </c>
+      <c r="F5" s="14">
         <f t="shared" si="1"/>
-        <v>0.143875</v>
+        <v>0.21317</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3564,21 +3411,21 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>18772</v>
+        <v>17482</v>
       </c>
       <c r="D6">
-        <v>1540</v>
+        <v>1510</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>20312</v>
-      </c>
-      <c r="F6" s="10">
+        <v>18992</v>
+      </c>
+      <c r="F6" s="14">
         <f t="shared" si="1"/>
-        <v>0.07003</v>
+        <v>0.066355</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3589,18 +3436,18 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>33341</v>
+        <v>37119</v>
       </c>
       <c r="D7">
-        <v>1395</v>
+        <v>1554</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>34736</v>
-      </c>
-      <c r="F7" s="10">
+        <v>38673</v>
+      </c>
+      <c r="F7" s="14">
         <f t="shared" si="1"/>
-        <v>0.1042775</v>
+        <v>0.1161075</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3611,18 +3458,18 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>8783</v>
+        <v>10027</v>
       </c>
       <c r="D8">
-        <v>719</v>
+        <v>1008</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>9502</v>
-      </c>
-      <c r="F8" s="10">
+        <v>11035</v>
+      </c>
+      <c r="F8" s="14">
         <f t="shared" si="1"/>
-        <v>0.0327425</v>
+        <v>0.0401875</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3633,18 +3480,18 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>5588</v>
+        <v>6305</v>
       </c>
       <c r="D9">
-        <v>294</v>
+        <v>369</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>5882</v>
-      </c>
-      <c r="F9" s="10">
+        <v>6674</v>
+      </c>
+      <c r="F9" s="14">
         <f t="shared" si="1"/>
-        <v>0.01838</v>
+        <v>0.0212975</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3655,18 +3502,18 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>10466</v>
+        <v>11646</v>
       </c>
       <c r="D10">
-        <v>628</v>
+        <v>826</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>11094</v>
-      </c>
-      <c r="F10" s="10">
+        <v>12472</v>
+      </c>
+      <c r="F10" s="14">
         <f t="shared" si="1"/>
-        <v>0.035585</v>
+        <v>0.041505</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3677,18 +3524,19 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>6283</v>
+        <f>10262-3092</f>
+        <v>7170</v>
       </c>
       <c r="D11">
         <v>229</v>
       </c>
       <c r="E11">
-        <f>C11+D11</f>
-        <v>6512</v>
-      </c>
-      <c r="F11" s="10">
+        <f t="shared" si="0"/>
+        <v>7399</v>
+      </c>
+      <c r="F11" s="14">
         <f t="shared" si="1"/>
-        <v>0.0191425</v>
+        <v>0.02136</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3716,7 +3564,7 @@
       <c r="H13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3724,15 +3572,15 @@
       <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <f>E27</f>
         <v>15</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>E28</f>
         <v>0</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <f>E29</f>
         <v>1</v>
       </c>
@@ -3748,367 +3596,381 @@
         <f>2*E14*F14/(E14+F14)</f>
         <v>0.967741935483871</v>
       </c>
-      <c r="H14" s="2">
-        <f>(I14-B14)/I14</f>
-        <v>0</v>
-      </c>
-      <c r="I14">
+      <c r="H14" s="11">
         <f>E30</f>
         <v>15</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" ref="I14:I23" si="2">(H14-B14)/H14</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <f>E32</f>
-        <v>15</v>
-      </c>
-      <c r="C15" s="12">
+        <v>14.3333333333333</v>
+      </c>
+      <c r="C15" s="11">
         <f>E33</f>
         <v>1</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <f>E34</f>
         <v>0.666666666666667</v>
       </c>
       <c r="E15" s="2">
-        <f t="shared" ref="E15:E23" si="2">B15/(B15+C15)</f>
-        <v>0.9375</v>
+        <f t="shared" ref="E15:E23" si="3">B15/(B15+C15)</f>
+        <v>0.934782608695652</v>
       </c>
       <c r="F15" s="2">
-        <f t="shared" ref="F15:F23" si="3">B15/(B15+D15)</f>
-        <v>0.957446808510638</v>
+        <f t="shared" ref="F15:F23" si="4">B15/(B15+D15)</f>
+        <v>0.955555555555556</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" ref="G15:G23" si="4">2*E15*F15/(E15+F15)</f>
-        <v>0.947368421052632</v>
-      </c>
-      <c r="H15" s="2">
-        <f t="shared" ref="H15:H23" si="5">(I15-B15)/I15</f>
-        <v>0.1</v>
-      </c>
-      <c r="I15" s="12">
+        <f t="shared" ref="G15:G23" si="5">2*E15*F15/(E15+F15)</f>
+        <v>0.945054945054945</v>
+      </c>
+      <c r="H15" s="11">
         <f>E35</f>
         <v>16.6666666666667</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="2"/>
+        <v>0.14</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <f>E37</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="11">
+        <f>E38</f>
         <v>3</v>
       </c>
-      <c r="C16" s="12">
-        <f>E38</f>
-        <v>5</v>
-      </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <f>E39</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="5"/>
+        <v>0.823529411764706</v>
+      </c>
+      <c r="H16" s="11">
+        <f>E40</f>
+        <v>11.6666666666667</v>
+      </c>
+      <c r="I16" s="5">
         <f t="shared" si="2"/>
-        <v>0.375</v>
-      </c>
-      <c r="F16" s="2">
-        <f t="shared" si="3"/>
-        <v>0.6</v>
-      </c>
-      <c r="G16" s="5">
-        <f t="shared" si="4"/>
-        <v>0.461538461538462</v>
-      </c>
-      <c r="H16" s="2">
-        <f t="shared" si="5"/>
-        <v>0.625</v>
-      </c>
-      <c r="I16" s="12">
-        <f>E40</f>
-        <v>8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <f>E42</f>
         <v>10</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>E43</f>
         <v>0</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="11">
         <f>E44</f>
         <v>0</v>
       </c>
       <c r="E17" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F17" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H17" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="12">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11">
         <f>E45</f>
         <v>10</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <f>E47</f>
         <v>3</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <f>E48</f>
         <v>0</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="11">
         <f>E49</f>
         <v>0</v>
       </c>
       <c r="E18" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F18" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H18" s="2">
         <f t="shared" si="5"/>
-        <v>0.4</v>
-      </c>
-      <c r="I18" s="12">
+        <v>1</v>
+      </c>
+      <c r="H18" s="11">
         <f>E50</f>
         <v>5</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <f>E52</f>
         <v>5</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <f>E53</f>
         <v>1</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <f>E54</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.833333333333333</v>
       </c>
       <c r="F19" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>0.833333333333333</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="4"/>
-        <v>0.909090909090909</v>
-      </c>
-      <c r="H19" s="2">
         <f t="shared" si="5"/>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I19" s="12">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="H19" s="11">
         <f>E55</f>
         <v>6</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="2"/>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <f>E57</f>
         <v>3</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <f>E58</f>
         <v>0</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="11">
         <f>E59</f>
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F20" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H20" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="12">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11">
         <f>E60</f>
         <v>3</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <f>E62</f>
         <v>2</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <f>E63</f>
         <v>0</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <f>E59</f>
         <v>0</v>
       </c>
       <c r="E21" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F21" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="12">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11">
         <f>E65</f>
         <v>2</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <f>E67</f>
         <v>3</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <f>E68</f>
         <v>0</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <f>E64</f>
         <v>0</v>
       </c>
       <c r="E22" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="F22" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H22" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="12">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11">
         <f>E70</f>
         <v>3</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <f>E72</f>
         <v>1</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <f>E73</f>
         <v>0</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="11">
         <f>E69</f>
         <v>0</v>
       </c>
       <c r="E23" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="11">
+        <f>E75</f>
+        <v>1</v>
+      </c>
+      <c r="I23" s="5">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="F23" s="2">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="G23" s="5">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="H23" s="2">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="12">
-        <f>E75</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="D24" s="9"/>
+      <c r="B24" s="12">
+        <f>AVERAGE(B14:B23)</f>
+        <v>6.33333333333333</v>
+      </c>
+      <c r="C24" s="12">
+        <f>AVERAGE(C14:C23)</f>
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="12">
+        <f>AVERAGE(D14:D23)</f>
+        <v>0.266666666666667</v>
+      </c>
       <c r="E24" s="5">
-        <f>AVERAGE(E14:E23)</f>
-        <v>0.914583333333333</v>
+        <f t="shared" ref="E24:I24" si="6">AVERAGE(E14:E23)</f>
+        <v>0.946811594202899</v>
       </c>
       <c r="F24" s="5">
-        <f>AVERAGE(F14:F23)</f>
-        <v>0.949494680851064</v>
+        <f t="shared" si="6"/>
+        <v>0.972638888888889</v>
       </c>
       <c r="G24" s="5">
-        <f>AVERAGE(G14:G23)</f>
-        <v>0.928573972716587</v>
-      </c>
-      <c r="H24" s="5">
-        <f>AVERAGE(H14:H23)</f>
-        <v>0.129166666666667</v>
-      </c>
-      <c r="I24" s="12"/>
+        <f t="shared" si="6"/>
+        <v>0.956965962563686</v>
+      </c>
+      <c r="H24" s="12">
+        <f t="shared" si="6"/>
+        <v>7.33333333333334</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="6"/>
+        <v>0.110666666666667</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
@@ -4128,7 +3990,7 @@
       <c r="D27">
         <v>15</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="11">
         <f>AVERAGE(B27:D27)</f>
         <v>15</v>
       </c>
@@ -4146,8 +4008,8 @@
       <c r="D28">
         <v>0</v>
       </c>
-      <c r="E28">
-        <f t="shared" ref="E28:E41" si="6">AVERAGE(B28:D28)</f>
+      <c r="E28" s="11">
+        <f t="shared" ref="E28:E41" si="7">AVERAGE(B28:D28)</f>
         <v>0</v>
       </c>
     </row>
@@ -4164,14 +4026,14 @@
       <c r="D29">
         <v>1</v>
       </c>
-      <c r="E29">
-        <f t="shared" si="6"/>
+      <c r="E29" s="11">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30">
         <v>15</v>
@@ -4182,8 +4044,8 @@
       <c r="D30">
         <v>15</v>
       </c>
-      <c r="E30">
-        <f>AVERAGE(B30:D30)</f>
+      <c r="E30" s="11">
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
     </row>
@@ -4191,6 +4053,7 @@
       <c r="A31" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="E31" s="11"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
@@ -4203,11 +4066,11 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>15</v>
-      </c>
-      <c r="E32" s="12">
-        <f t="shared" si="6"/>
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="E32" s="11">
+        <f t="shared" si="7"/>
+        <v>14.3333333333333</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -4223,8 +4086,8 @@
       <c r="D33">
         <v>2</v>
       </c>
-      <c r="E33">
-        <f t="shared" si="6"/>
+      <c r="E33" s="11">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -4241,14 +4104,14 @@
       <c r="D34">
         <v>1</v>
       </c>
-      <c r="E34" s="12">
-        <f t="shared" si="6"/>
+      <c r="E34" s="11">
+        <f t="shared" si="7"/>
         <v>0.666666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35">
         <v>15</v>
@@ -4259,8 +4122,8 @@
       <c r="D35">
         <v>16</v>
       </c>
-      <c r="E35" s="12">
-        <f>AVERAGE(B35:D35)</f>
+      <c r="E35" s="11">
+        <f t="shared" si="7"/>
         <v>16.6666666666667</v>
       </c>
     </row>
@@ -4268,23 +4131,24 @@
       <c r="A36" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="E36" s="11"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D37">
-        <v>3</v>
-      </c>
-      <c r="E37">
-        <f t="shared" si="6"/>
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="E37" s="11">
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -4292,17 +4156,17 @@
         <v>22</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>5</v>
-      </c>
-      <c r="E38">
-        <f t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="E38" s="11">
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4310,41 +4174,42 @@
         <v>23</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>2</v>
-      </c>
-      <c r="E39">
-        <f t="shared" si="6"/>
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E39" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D40">
-        <v>8</v>
-      </c>
-      <c r="E40">
-        <f>AVERAGE(B40:D40)</f>
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="E40" s="11">
+        <f t="shared" si="7"/>
+        <v>11.6666666666667</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="E41" s="11"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="1" t="s">
@@ -4359,7 +4224,7 @@
       <c r="D42">
         <v>10</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="11">
         <f>AVERAGE(B42:D42)</f>
         <v>10</v>
       </c>
@@ -4377,8 +4242,8 @@
       <c r="D43">
         <v>0</v>
       </c>
-      <c r="E43">
-        <f t="shared" ref="E43:E74" si="7">AVERAGE(B43:D43)</f>
+      <c r="E43" s="11">
+        <f t="shared" ref="E43:E75" si="8">AVERAGE(B43:D43)</f>
         <v>0</v>
       </c>
     </row>
@@ -4395,14 +4260,14 @@
       <c r="D44">
         <v>0</v>
       </c>
-      <c r="E44">
-        <f t="shared" si="7"/>
+      <c r="E44" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B45">
         <v>10</v>
@@ -4413,8 +4278,8 @@
       <c r="D45">
         <v>10</v>
       </c>
-      <c r="E45">
-        <f>AVERAGE(B45:D45)</f>
+      <c r="E45" s="11">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
@@ -4422,6 +4287,7 @@
       <c r="A46" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="1" t="s">
@@ -4436,8 +4302,8 @@
       <c r="D47">
         <v>3</v>
       </c>
-      <c r="E47">
-        <f t="shared" si="7"/>
+      <c r="E47" s="11">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
@@ -4454,8 +4320,8 @@
       <c r="D48">
         <v>0</v>
       </c>
-      <c r="E48">
-        <f t="shared" si="7"/>
+      <c r="E48" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -4472,14 +4338,14 @@
       <c r="D49">
         <v>0</v>
       </c>
-      <c r="E49">
-        <f t="shared" si="7"/>
+      <c r="E49" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B50">
         <v>5</v>
@@ -4490,8 +4356,8 @@
       <c r="D50">
         <v>5</v>
       </c>
-      <c r="E50">
-        <f>AVERAGE(B50:D50)</f>
+      <c r="E50" s="11">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
@@ -4499,6 +4365,7 @@
       <c r="A51" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="E51" s="11"/>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="1" t="s">
@@ -4513,8 +4380,8 @@
       <c r="D52">
         <v>5</v>
       </c>
-      <c r="E52">
-        <f t="shared" si="7"/>
+      <c r="E52" s="11">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
@@ -4531,8 +4398,8 @@
       <c r="D53">
         <v>1</v>
       </c>
-      <c r="E53">
-        <f t="shared" si="7"/>
+      <c r="E53" s="11">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -4541,22 +4408,22 @@
         <v>23</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E54" s="11">
+        <f t="shared" si="8"/>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B55">
         <v>6</v>
@@ -4567,8 +4434,8 @@
       <c r="D55">
         <v>6</v>
       </c>
-      <c r="E55">
-        <f>AVERAGE(B55:D55)</f>
+      <c r="E55" s="11">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
@@ -4576,6 +4443,7 @@
       <c r="A56" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="E56" s="11"/>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="1" t="s">
@@ -4590,8 +4458,8 @@
       <c r="D57">
         <v>3</v>
       </c>
-      <c r="E57">
-        <f t="shared" si="7"/>
+      <c r="E57" s="11">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
@@ -4608,8 +4476,8 @@
       <c r="D58">
         <v>0</v>
       </c>
-      <c r="E58">
-        <f t="shared" si="7"/>
+      <c r="E58" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -4626,14 +4494,14 @@
       <c r="D59">
         <v>0</v>
       </c>
-      <c r="E59">
-        <f t="shared" si="7"/>
+      <c r="E59" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B60">
         <v>3</v>
@@ -4644,7 +4512,7 @@
       <c r="D60">
         <v>3</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="11">
         <v>3</v>
       </c>
     </row>
@@ -4652,6 +4520,7 @@
       <c r="A61" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="E61" s="11"/>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="1" t="s">
@@ -4666,8 +4535,8 @@
       <c r="D62">
         <v>2</v>
       </c>
-      <c r="E62">
-        <f t="shared" si="7"/>
+      <c r="E62" s="11">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
@@ -4684,8 +4553,8 @@
       <c r="D63">
         <v>0</v>
       </c>
-      <c r="E63">
-        <f t="shared" si="7"/>
+      <c r="E63" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -4702,14 +4571,14 @@
       <c r="D64">
         <v>0</v>
       </c>
-      <c r="E64">
-        <f t="shared" si="7"/>
+      <c r="E64" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B65">
         <v>2</v>
@@ -4720,8 +4589,8 @@
       <c r="D65">
         <v>2</v>
       </c>
-      <c r="E65">
-        <f>AVERAGE(B65:D65)</f>
+      <c r="E65" s="11">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
@@ -4729,6 +4598,7 @@
       <c r="A66" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="E66" s="11"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="1" t="s">
@@ -4743,8 +4613,8 @@
       <c r="D67">
         <v>3</v>
       </c>
-      <c r="E67">
-        <f t="shared" si="7"/>
+      <c r="E67" s="11">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
@@ -4761,8 +4631,8 @@
       <c r="D68">
         <v>0</v>
       </c>
-      <c r="E68">
-        <f t="shared" si="7"/>
+      <c r="E68" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -4779,14 +4649,14 @@
       <c r="D69">
         <v>0</v>
       </c>
-      <c r="E69">
-        <f t="shared" si="7"/>
+      <c r="E69" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B70">
         <v>3</v>
@@ -4797,8 +4667,8 @@
       <c r="D70">
         <v>3</v>
       </c>
-      <c r="E70">
-        <f>AVERAGE(B70:D70)</f>
+      <c r="E70" s="11">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
@@ -4806,6 +4676,7 @@
       <c r="A71" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="E71" s="11"/>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="1" t="s">
@@ -4820,8 +4691,8 @@
       <c r="D72">
         <v>1</v>
       </c>
-      <c r="E72">
-        <f t="shared" si="7"/>
+      <c r="E72" s="11">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -4838,8 +4709,8 @@
       <c r="D73">
         <v>0</v>
       </c>
-      <c r="E73">
-        <f t="shared" si="7"/>
+      <c r="E73" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -4856,14 +4727,14 @@
       <c r="D74">
         <v>0</v>
       </c>
-      <c r="E74">
-        <f t="shared" si="7"/>
+      <c r="E74" s="11">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -4874,8 +4745,8 @@
       <c r="D75">
         <v>1</v>
       </c>
-      <c r="E75">
-        <f>AVERAGE(B75:D75)</f>
+      <c r="E75" s="11">
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
     </row>
@@ -4888,345 +4759,1464 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:I75"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="32.3653846153846" customWidth="1"/>
-    <col min="2" max="2" width="8.49038461538461" customWidth="1"/>
+    <col min="1" max="1" width="31.7307692307692" customWidth="1"/>
+    <col min="2" max="2" width="14.4230769230769" customWidth="1"/>
+    <col min="3" max="3" width="12.6538461538462" customWidth="1"/>
+    <col min="4" max="4" width="12.8076923076923" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>89403</v>
       </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5">
-        <f t="shared" ref="F2:F11" si="0">1-H2</f>
-        <v>0.5625</v>
-      </c>
-      <c r="G2" s="5">
-        <f>2*E2*F2/(E2+F2)</f>
-        <v>0.72</v>
-      </c>
-      <c r="H2" s="2">
-        <f>D2/(B2+D2)</f>
-        <v>0.4375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>5983</v>
+      </c>
+      <c r="E2">
+        <f>C2+D2</f>
+        <v>95386</v>
+      </c>
+      <c r="F2" s="14">
+        <f>C2*(5/1000000)+D2*(25/1000000)</f>
+        <v>0.59659</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>101454</v>
       </c>
       <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="5">
-        <f t="shared" ref="G3:G11" si="1">2*E3*F3/(E3+F3)</f>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="H3" s="2">
-        <f t="shared" ref="H3:H11" si="2">D3/(B3+D3)</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>6949</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E11" si="0">C3+D3</f>
+        <v>108403</v>
+      </c>
+      <c r="F3" s="14">
+        <f t="shared" ref="F3:F11" si="1">C3*(5/1000000)+D3*(25/1000000)</f>
+        <v>0.680995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100037</v>
       </c>
       <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
+        <v>7560</v>
+      </c>
+      <c r="E4">
         <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="G4" s="5">
+        <v>107597</v>
+      </c>
+      <c r="F4" s="14">
         <f t="shared" si="1"/>
-        <v>0.571428571428572</v>
-      </c>
-      <c r="H4" s="2">
-        <f t="shared" si="2"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>0.689185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>81083</v>
       </c>
       <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5">
+        <v>5843</v>
+      </c>
+      <c r="E5">
         <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="G5" s="5">
+        <v>86926</v>
+      </c>
+      <c r="F5" s="14">
         <f t="shared" si="1"/>
-        <v>0.888888888888889</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>0.55149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>21181</v>
       </c>
       <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5">
+        <v>1909</v>
+      </c>
+      <c r="E6">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="5">
+        <v>23090</v>
+      </c>
+      <c r="F6" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H6" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>0.15363</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>50166</v>
       </c>
       <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="F7" s="5">
+        <v>3356</v>
+      </c>
+      <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="5">
+        <v>53522</v>
+      </c>
+      <c r="F7" s="14">
         <f t="shared" si="1"/>
-        <v>0.6</v>
-      </c>
-      <c r="H7" s="2">
-        <f t="shared" si="2"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>0.33473</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>12248</v>
       </c>
       <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1</v>
-      </c>
-      <c r="F8" s="5">
+        <v>1193</v>
+      </c>
+      <c r="E8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
+        <v>13441</v>
+      </c>
+      <c r="F8" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H8" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>0.091065</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>7623</v>
       </c>
       <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1</v>
-      </c>
-      <c r="F9" s="5">
+        <v>479</v>
+      </c>
+      <c r="E9">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G9" s="5">
+        <v>8102</v>
+      </c>
+      <c r="F9" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>0.05009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>14097</v>
       </c>
       <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5">
+        <v>1056</v>
+      </c>
+      <c r="E10">
         <f t="shared" si="0"/>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="G10" s="5">
+        <v>15153</v>
+      </c>
+      <c r="F10" s="14">
         <f t="shared" si="1"/>
-        <v>0.8</v>
-      </c>
-      <c r="H10" s="2">
-        <f t="shared" si="2"/>
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>0.096885</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>8073</v>
       </c>
       <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5">
+        <v>315</v>
+      </c>
+      <c r="E11">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G11" s="5">
+        <v>8388</v>
+      </c>
+      <c r="F11" s="14">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H11" s="2">
+        <v>0.04824</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="10">
+        <f>E27</f>
+        <v>15</v>
+      </c>
+      <c r="C14" s="11">
+        <f>E28</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="11">
+        <f>E29</f>
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" ref="E14:E23" si="2">B14/(B14+C14)</f>
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" ref="F14:F23" si="3">B14/(B14+D14)</f>
+        <v>0.9375</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" ref="G14:G23" si="4">2*E14*F14/(E14+F14)</f>
+        <v>0.967741935483871</v>
+      </c>
+      <c r="H14" s="11">
+        <f>E30</f>
+        <v>15</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" ref="I14:I23" si="5">(H14-B14)/H14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="10">
+        <f>E32</f>
+        <v>13</v>
+      </c>
+      <c r="C15" s="11">
+        <f>E33</f>
+        <v>2</v>
+      </c>
+      <c r="D15" s="11">
+        <f>E34</f>
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="D12" s="9">
-        <f>AVERAGE(D2:D11)</f>
-        <v>2.7</v>
-      </c>
-      <c r="E12" s="5">
-        <f>AVERAGE(E2:E11)</f>
-        <v>0.975</v>
-      </c>
-      <c r="F12" s="5">
-        <f>AVERAGE(F2:F11)</f>
-        <v>0.742916666666667</v>
-      </c>
-      <c r="G12" s="5">
-        <f>AVERAGE(G2:G11)</f>
-        <v>0.824698412698413</v>
+        <v>0.866666666666667</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="3"/>
+        <v>0.928571428571429</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" si="4"/>
+        <v>0.896551724137931</v>
+      </c>
+      <c r="H15" s="11">
+        <f>E35</f>
+        <v>18</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="5"/>
+        <v>0.277777777777778</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="10">
+        <f>E37</f>
+        <v>7.66666666666667</v>
+      </c>
+      <c r="C16" s="11">
+        <f>E38</f>
+        <v>2.33333333333333</v>
+      </c>
+      <c r="D16" s="11">
+        <f>E39</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="2"/>
+        <v>0.766666666666667</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="4"/>
+        <v>0.867924528301887</v>
+      </c>
+      <c r="H16" s="11">
+        <f>E40</f>
+        <v>10.6666666666667</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="5"/>
+        <v>0.28125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="10">
+        <f>E42</f>
+        <v>10</v>
+      </c>
+      <c r="C17" s="11">
+        <f>E43</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="11">
+        <f>E44</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H17" s="11">
+        <f>E45</f>
+        <v>12</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="5"/>
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="10">
+        <f>E47</f>
+        <v>3</v>
+      </c>
+      <c r="C18" s="11">
+        <f>E48</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="11">
+        <f>E49</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="11">
+        <f>E50</f>
+        <v>5</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="10">
+        <f>E52</f>
+        <v>5</v>
+      </c>
+      <c r="C19" s="11">
+        <f>E53</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="11">
+        <f>E54</f>
+        <v>2</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="3"/>
+        <v>0.714285714285714</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="4"/>
+        <v>0.833333333333333</v>
+      </c>
+      <c r="H19" s="11">
+        <f>E55</f>
+        <v>6</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="5"/>
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="10">
+        <f>E57</f>
+        <v>3</v>
+      </c>
+      <c r="C20" s="11">
+        <f>E58</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="11">
+        <f>E59</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="11">
+        <f>E60</f>
+        <v>3</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="10">
+        <f>E62</f>
+        <v>2</v>
+      </c>
+      <c r="C21" s="11">
+        <f>E63</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="11">
+        <f>E59</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H21" s="11">
+        <f>E65</f>
+        <v>2</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="10">
+        <f>E67</f>
+        <v>3</v>
+      </c>
+      <c r="C22" s="11">
+        <f>E68</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="11">
+        <f>E64</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H22" s="11">
+        <f>E70</f>
+        <v>3</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="10">
+        <f>E72</f>
+        <v>1</v>
+      </c>
+      <c r="C23" s="11">
+        <f>E73</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="11">
+        <f>E69</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H23" s="11">
+        <f>E75</f>
+        <v>1</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="B24" s="12">
+        <f>AVERAGE(B14:B23)</f>
+        <v>6.26666666666667</v>
+      </c>
+      <c r="C24" s="12">
+        <f>AVERAGE(C14:C23)</f>
+        <v>0.433333333333333</v>
+      </c>
+      <c r="D24" s="12">
+        <f>AVERAGE(D14:D23)</f>
+        <v>0.4</v>
+      </c>
+      <c r="E24" s="5">
+        <f t="shared" ref="E24:I24" si="6">AVERAGE(E14:E23)</f>
+        <v>0.963333333333333</v>
+      </c>
+      <c r="F24" s="5">
+        <f t="shared" si="6"/>
+        <v>0.958035714285714</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" si="6"/>
+        <v>0.956555152125702</v>
+      </c>
+      <c r="H24" s="12">
+        <f t="shared" si="6"/>
+        <v>7.56666666666667</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="6"/>
+        <v>0.129236111111111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>15</v>
+      </c>
+      <c r="E27" s="11">
+        <f t="shared" ref="E27:E30" si="7">AVERAGE(B27:D27)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" s="11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>15</v>
+      </c>
+      <c r="C30">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>15</v>
+      </c>
+      <c r="E30" s="11">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="11"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32">
+        <v>13</v>
+      </c>
+      <c r="C32">
+        <v>13</v>
+      </c>
+      <c r="D32">
+        <v>13</v>
+      </c>
+      <c r="E32" s="11">
+        <f t="shared" ref="E32:E35" si="8">AVERAGE(B32:D32)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" s="11">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" s="11">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35">
+        <v>18</v>
+      </c>
+      <c r="C35">
+        <v>18</v>
+      </c>
+      <c r="D35">
+        <v>18</v>
+      </c>
+      <c r="E35" s="11">
+        <f t="shared" si="8"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="11"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>8</v>
+      </c>
+      <c r="D37">
+        <v>8</v>
+      </c>
+      <c r="E37" s="11">
+        <f t="shared" ref="E37:E40" si="9">AVERAGE(B37:D37)</f>
+        <v>7.66666666666667</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38" s="11">
+        <f t="shared" si="9"/>
+        <v>2.33333333333333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39" s="11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40">
+        <v>11</v>
+      </c>
+      <c r="D40">
+        <v>11</v>
+      </c>
+      <c r="E40" s="11">
+        <f t="shared" si="9"/>
+        <v>10.6666666666667</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="11"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42">
+        <v>10</v>
+      </c>
+      <c r="C42">
+        <v>10</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42" s="11">
+        <f t="shared" ref="E42:E45" si="10">AVERAGE(B42:D42)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" s="11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>12</v>
+      </c>
+      <c r="D45">
+        <v>12</v>
+      </c>
+      <c r="E45" s="11">
+        <f t="shared" si="10"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="11"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47">
+        <v>3</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" s="11">
+        <f t="shared" ref="E47:E50" si="11">AVERAGE(B47:D47)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49" s="11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+      <c r="D50">
+        <v>5</v>
+      </c>
+      <c r="E50" s="11">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="11"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52">
+        <v>5</v>
+      </c>
+      <c r="C52">
+        <v>5</v>
+      </c>
+      <c r="D52">
+        <v>5</v>
+      </c>
+      <c r="E52" s="11">
+        <f t="shared" ref="E52:E55" si="12">AVERAGE(B52:D52)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53" s="11">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54" s="11">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55">
+        <v>6</v>
+      </c>
+      <c r="C55">
+        <v>6</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+      <c r="E55" s="11">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="11"/>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57" s="11">
+        <f t="shared" ref="E57:E59" si="13">AVERAGE(B57:D57)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59" s="11">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="11"/>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+      <c r="E62" s="11">
+        <f t="shared" ref="E62:E65" si="14">AVERAGE(B62:D62)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63" s="11">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64" s="11">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>2</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65" s="11">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="11"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>3</v>
+      </c>
+      <c r="E67" s="11">
+        <f t="shared" ref="E67:E70" si="15">AVERAGE(B67:D67)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68" s="11">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69" s="11">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>27</v>
+      </c>
+      <c r="B70">
+        <v>3</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70">
+        <v>3</v>
+      </c>
+      <c r="E70" s="11">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" s="11"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>1</v>
+      </c>
+      <c r="E72" s="11">
+        <f t="shared" ref="E72:E75" si="16">AVERAGE(B72:D72)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73" s="11">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74" s="11">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+      <c r="E75" s="11">
+        <f t="shared" si="16"/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5236,6 +6226,646 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="32.3653846153846" customWidth="1"/>
+    <col min="2" max="2" width="8.49038461538461" customWidth="1"/>
+    <col min="7" max="7" width="12.9230769230769"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5">
+        <f t="shared" ref="F2:F11" si="0">1-H2</f>
+        <v>0.5625</v>
+      </c>
+      <c r="G2" s="5">
+        <f>2*E2*F2/(E2+F2)</f>
+        <v>0.72</v>
+      </c>
+      <c r="H2" s="2">
+        <f>D2/(B2+D2)</f>
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="5">
+        <f t="shared" ref="G3:G11" si="1">2*E3*F3/(E3+F3)</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="H3" s="2">
+        <f t="shared" ref="H3:H11" si="2">D3/(B3+D3)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="1"/>
+        <v>0.571428571428572</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" si="2"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="5">
+        <f t="shared" si="1"/>
+        <v>0.888888888888889</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="5">
+        <f t="shared" si="1"/>
+        <v>0.6</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="G10" s="5">
+        <f t="shared" si="1"/>
+        <v>0.8</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="2"/>
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" s="9">
+        <f>AVERAGE(B2:B11)</f>
+        <v>4.2</v>
+      </c>
+      <c r="C12" s="9">
+        <f>AVERAGE(C2:C11)</f>
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="9">
+        <f>AVERAGE(D2:D11)</f>
+        <v>2.7</v>
+      </c>
+      <c r="E12" s="5">
+        <f>AVERAGE(E2:E11)</f>
+        <v>0.975</v>
+      </c>
+      <c r="F12" s="5">
+        <f>AVERAGE(F2:F11)</f>
+        <v>0.742916666666667</v>
+      </c>
+      <c r="G12" s="5">
+        <f>AVERAGE(G2:G11)</f>
+        <v>0.824698412698413</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="10">
+        <v>15</v>
+      </c>
+      <c r="C15" s="11">
+        <v>0</v>
+      </c>
+      <c r="D15" s="11">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.967741935483871</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="10">
+        <v>14.3333333333333</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.934782608695652</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.955555555555556</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.945054945054945</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="10">
+        <v>7</v>
+      </c>
+      <c r="C17" s="11">
+        <v>3</v>
+      </c>
+      <c r="D17" s="11">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.823529411764706</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="10">
+        <v>10</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="10">
+        <v>3</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0</v>
+      </c>
+      <c r="D19" s="11">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="10">
+        <v>5</v>
+      </c>
+      <c r="C20" s="11">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.833333333333333</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="10">
+        <v>3</v>
+      </c>
+      <c r="C21" s="11">
+        <v>0</v>
+      </c>
+      <c r="D21" s="11">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="10">
+        <v>2</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0</v>
+      </c>
+      <c r="D22" s="11">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="10">
+        <v>3</v>
+      </c>
+      <c r="C23" s="11">
+        <v>0</v>
+      </c>
+      <c r="D23" s="11">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="10">
+        <v>1</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0</v>
+      </c>
+      <c r="D24" s="11">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="B25" s="12">
+        <v>6.33333333333333</v>
+      </c>
+      <c r="C25" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="12">
+        <v>0.266666666666667</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.946811594202899</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.972638888888889</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0.956965962563686</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L187"/>
@@ -10221,7 +11851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G19"/>
@@ -10502,7 +12132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G11"/>
@@ -10775,7 +12405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G11"/>
